--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -24509,7 +24509,7 @@
           <t>B | 597呎 (2房)
 $1,967万
 $32,942/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
@@ -24591,7 +24591,7 @@
           <t>B | 597呎 (2房)
 $1,928万
 $32,295/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -8,10 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -114,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2014,7 +1869,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -5006,7 +4861,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5578,7 +5433,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -6498,7 +6353,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6728,7 +6583,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6958,7 +6813,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7188,7 +7043,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7418,7 +7273,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7648,7 +7503,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -8108,7 +7963,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8798,7 +8653,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -9028,7 +8883,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9212,7 +9067,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9442,7 +9297,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9488,7 +9343,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9718,7 +9573,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -10868,7 +10723,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -13856,7 +13711,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13902,7 +13757,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -14044,7 +13899,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -14666,7 +14521,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14812,7 +14667,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -15054,7 +14909,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -15200,7 +15055,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -15392,7 +15247,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15438,7 +15293,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -17444,7 +17299,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -17628,7 +17483,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -17858,7 +17713,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -17904,7 +17759,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -18134,7 +17989,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -18364,7 +18219,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -18594,7 +18449,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -18824,7 +18679,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -19008,7 +18863,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -19054,7 +18909,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -19284,7 +19139,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -19422,7 +19277,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -19514,7 +19369,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -19744,7 +19599,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -19974,7 +19829,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -20204,7 +20059,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -20296,7 +20151,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -20342,7 +20197,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -20434,7 +20289,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -20526,7 +20381,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -20572,7 +20427,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -20664,7 +20519,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -20802,7 +20657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -20894,7 +20749,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -21124,7 +20979,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -21216,7 +21071,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -21354,7 +21209,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -21560,4969 +21415,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑜一．天海 - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>99 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>80 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>MAISON A</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>MAISON B</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>MAISON C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1564呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1564呎 (4+房)
-$7,273万
-$46,500/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,533万
-$36,500/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$2,075万
-$35,105/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$2,075万
-$35,105/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$4,034万
-$40,500/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,485万
-$36,000/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$2,130万
-$36,045/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$2,066万
-$34,964/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,984万
-$40,000/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$11,280万
-$116,529/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$11,280万
-$190,863/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$11,280万
-$190,863/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$11,280万
-$113,253/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,509万
-$36,250/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$2,002万
-$33,871/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$2,002万
-$33,871/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,884万
-$39,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,320万
-$34,298/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,970万
-$33,337/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,970万
-$33,337/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,830万
-$38,454/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,272万
-$33,800/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,939万
-$32,813/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,939万
-$32,813/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,795万
-$38,100/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,223万
-$33,300/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,909万
-$36,356/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,909万
-$32,296/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,792万
-$38,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,293万
-$34,021/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,879万
-$31,788/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,879万
-$31,788/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,741万
-$37,563/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,533万
-$36,500/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,956万
-$33,093/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$2,081万
-$35,212/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,175万
-$32,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,891万
-$31,995/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,891万
-$31,995/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,486万
-$35,000/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,078万
-$31,798/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,853万
-$31,346/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,853万
-$31,346/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,436万
-$34,500/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-      <c r="H18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$3,030万
-$31,300/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,842万
-$31,159/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,842万
-$31,159/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,436万
-$34,500/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-      <c r="H19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,981万
-$30,800/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,832万
-$31,004/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,832万
-$31,004/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,406万
-$34,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,933万
-$30,300/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,934万
-$32,726/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,866万
-$31,576/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,685万
-$37,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-      <c r="H21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,885万
-$29,800/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,924万
-$32,563/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,814万
-$30,696/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-$3,546万
-$35,600/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr"/>
-      <c r="G22" s="17" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,885万
-$29,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,906万
-$32,242/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,796万
-$30,393/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-      <c r="H23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,875万
-$29,700/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,817万
-$30,748/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,747万
-$29,564/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr"/>
-      <c r="G24" s="17" t="inlineStr"/>
-      <c r="H24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,768万
-$28,600/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,685万
-$28,505/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,685万
-$28,505/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr"/>
-      <c r="G25" s="17" t="inlineStr"/>
-      <c r="H25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,860万
-$29,550/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,663万
-$28,141/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr"/>
-      <c r="G26" s="17" t="inlineStr"/>
-      <c r="H26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-$2,681万
-$27,700/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,671万
-$28,279/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,623万
-$27,454/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
-      <c r="G27" s="17" t="inlineStr"/>
-      <c r="H27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,583万
-$26,784/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr"/>
-      <c r="G28" s="17" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 968呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 591呎 (2房)
-$1,583万
-$26,785/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,537万
-$26,005/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr"/>
-      <c r="G29" s="17" t="inlineStr"/>
-      <c r="H29" s="17" t="inlineStr"/>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 925呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 548呎 (2房)
-$1,660万
-$30,292/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 548呎 (2房)
-$1,708万
-$31,168/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 953呎 (3房)
-$3,383万
-$35,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr"/>
-      <c r="G30" s="17" t="inlineStr"/>
-      <c r="H30" s="17" t="inlineStr"/>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr"/>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr"/>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>MAISON A | 1108呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>MAISON B | 967呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>MAISON C | 967呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑜一．天海 - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>125 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>124 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$835万
-$25,061/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$839万
-$24,820/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,460万
-$26,995/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$987万
-$27,116/呎
-(23年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 959呎 (3房)
-$2,976万
-$31,032/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$775万
-$23,260/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$779万
-$23,058/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,373万
-$25,380/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$893万
-$24,524/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,201万
-$33,348/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$770万
-$23,119/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$775万
-$22,918/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,360万
-$25,130/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$765万
-$21,026/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 959呎 (3房)
-$2,880万
-$30,031/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$768万
-$23,048/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$772万
-$22,851/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,394万
-$25,769/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$887万
-$24,377/呎
-(23年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,832万
-$29,500/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$765万
-$22,980/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$770万
-$22,782/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,333万
-$24,635/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$895万
-$24,590/呎
-(23年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,098万
-$32,266/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$763万
-$22,912/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$768万
-$22,715/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,320万
-$24,391/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$913万
-$25,085/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,736万
-$28,500/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$761万
-$22,841/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$765万
-$22,645/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,307万
-$24,150/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 365呎 (1房)
-$910万
-$24,941/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,771万
-$28,866/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$758万
-$22,776/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$763万
-$22,578/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,294万
-$23,911/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$908万
-$24,937/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,659万
-$27,700/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$764万
-$22,942/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 943呎 (1房)
-$761万
-$8,069/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,281万
-$23,674/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$905万
-$24,862/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,707万
-$28,196/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$762万
-$22,871/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$759万
-$22,441/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,253万
-$23,160/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$872万
-$23,942/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,592万
-$27,000/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$757万
-$22,742/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$759万
-$22,441/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,253万
-$23,160/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$902万
-$24,787/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,058万
-$31,854/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$749万
-$22,503/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$754万
-$22,309/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,228万
-$22,700/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 365呎 (1房)
-$897万
-$24,570/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,544万
-$26,500/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$747万
-$22,438/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$752万
-$22,240/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,209万
-$22,355/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$894万
-$24,567/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,515万
-$26,200/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$745万
-$22,370/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$749万
-$22,173/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,191万
-$22,014/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$861万
-$23,657/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 959呎 (3房)
-$2,486万
-$25,927/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$746万
-$22,400/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$747万
-$22,108/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,173万
-$21,674/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$888万
-$24,396/呎
-(23年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,477万
-$25,800/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$740万
-$22,236/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$745万
-$22,044/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,169万
-$21,609/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$854万
-$23,468/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,867万
-$29,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$738万
-$22,170/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$743万
-$21,977/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,166万
-$21,543/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$880万
-$24,176/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,924万
-$30,459/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$736万
-$22,102/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$741万
-$21,909/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,147万
-$21,208/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$738万
-$20,262/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,764万
-$28,788/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$741万
-$22,266/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$750万
-$22,199/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,147万
-$21,208/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$863万
-$23,702/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,256万
-$23,500/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$737万
-$22,129/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$736万
-$21,780/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,144万
-$21,144/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$859万
-$23,586/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,208万
-$23,000/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$737万
-$22,130/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$734万
-$21,713/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,126万
-$20,811/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$730万
-$20,059/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,131万
-$22,200/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$727万
-$21,840/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$732万
-$21,649/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,086万
-$20,074/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$727万
-$19,961/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,504万
-$26,081/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$720万
-$21,623/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$721万
-$21,323/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,046万
-$19,342/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$809万
-$22,221/呎
-(24年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2,064万
-$21,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$721万
-$21,639/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$711万
-$21,040/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1,022万
-$18,888/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$799万
-$21,948/呎
-(24年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 916呎 (3房)
-$2,843万
-$31,034/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 311呎 (1房)
-$787万
-$25,308/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 317呎 (1房)
-$805万
-$25,403/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 504呎 (2房)
-$1,143万
-$22,688/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 327呎 (1房)
-$863万
-$26,400/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑜一．天海 - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>98 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>40 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>MAISON D</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>MAISON E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>A | 1615呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>B | 1556呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 1615呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 1556呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,639万
-$36,500/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$2,138万
-$35,807/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$2,152万
-$36,046/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$2,154万
-$36,089/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$2,022万
-$33,871/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$2,374万
-$40,039/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,420万
-$34,301/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,990万
-$33,337/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,959万
-$32,814/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,967万
-$32,942/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,947万
-$32,832/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,898万
-$31,789/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,928万
-$32,295/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,210万
-$32,201/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,883万
-$31,536/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$2,215万
-$37,352/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,170万
-$31,800/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,871万
-$31,347/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$2,202万
-$37,130/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,121万
-$31,300/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,876万
-$31,419/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,071万
-$30,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,851万
-$31,005/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3,021万
-$30,301/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,923万
-$32,205/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,907万
-$32,156/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2,971万
-$29,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,869万
-$31,310/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,833万
-$30,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr"/>
-      <c r="G22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2,921万
-$29,301/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,836万
-$30,960/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,765万
-$29,564/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,786万
-$30,117/呎
-(24年-02月)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr"/>
-      <c r="G24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,789万
-$29,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr"/>
-      <c r="G25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,680万
-$28,141/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,723万
-$29,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr"/>
-      <c r="G26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,657万
-$27,762/呎
-(23年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
-      <c r="G27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,581万
-$26,487/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,624万
-$27,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr"/>
-      <c r="G28" s="17" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1,589万
-$26,622/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1,576万
-$26,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr"/>
-      <c r="G29" s="17" t="inlineStr"/>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 954呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 555呎 (2房)
-$1,988万
-$35,823/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,957万
-$35,589/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 949呎 (3房)
-$3,421万
-$36,048/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr"/>
-      <c r="G30" s="17" t="inlineStr"/>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr"/>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr"/>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>MAISON D | 889呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>MAISON E | 940呎 (3房)
-$2,880万
-$30,638/呎
-(23年-11月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑜一．天海 - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>125 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>121 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1144呎 (3房)
-$4,777万
-$41,757/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 425呎 (2房)
-$1,384万
-$32,572/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 425呎 (2房)
-$1,357万
-$31,928/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 1116呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,314万
-$28,006/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,399万
-$26,654/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,483万
-$28,407/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$3,064万
-$32,735/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,270万
-$27,077/呎
-(23年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,437万
-$27,377/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,454万
-$27,850/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$3,017万
-$32,234/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,124万
-$23,955/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$3,067万
-$32,050/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,345万
-$25,621/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,425万
-$27,303/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,970万
-$31,734/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,117万
-$23,812/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,319万
-$25,118/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,410万
-$27,008/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,783万
-$29,732/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,110万
-$23,669/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,828万
-$29,550/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,293万
-$24,626/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,385万
-$26,537/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,736万
-$29,231/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,104万
-$23,529/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,780万
-$29,050/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,283万
-$24,430/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,374万
-$26,327/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,689万
-$28,731/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,247万
-$26,587/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$3,030万
-$31,659/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,587万
-$30,232/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,363万
-$26,118/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,642万
-$28,230/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,268万
-$27,042/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,909万
-$30,397/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,247万
-$23,755/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,240万
-$23,752/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,595万
-$27,729/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,090万
-$23,238/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,994万
-$31,283/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,237万
-$23,566/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,491万
-$28,563/呎
-(23年-09月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 937呎 (3房)
-$2,549万
-$27,200/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,253万
-$26,721/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,589万
-$27,050/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,237万
-$23,566/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,230万
-$23,565/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 937呎 (3房)
-$2,502万
-$26,700/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,232万
-$26,265/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,560万
-$26,750/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,225万
-$23,333/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,218万
-$23,332/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,474万
-$26,427/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,203万
-$25,656/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,874万
-$30,030/呎
-(23年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,219万
-$23,216/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,212万
-$23,214/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,441万
-$26,078/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,242万
-$26,481/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,923万
-$30,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,213万
-$23,101/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,206万
-$23,098/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,417万
-$25,827/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,238万
-$26,402/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,474万
-$25,850/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,250万
-$23,806/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,257万
-$24,079/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,389万
-$25,527/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,231万
-$26,244/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,445万
-$25,550/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,490万
-$28,383/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,230万
-$23,562/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 937呎 (3房)
-$2,361万
-$25,200/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,224万
-$26,088/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,383万
-$24,900/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,177万
-$22,422/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,170万
-$22,421/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 937呎 (3房)
-$2,314万
-$24,700/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,196万
-$25,491/呎
-(23年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,378万
-$24,850/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,201万
-$22,880/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,153万
-$22,088/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 937呎 (3房)
-$2,268万
-$24,200/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,209万
-$25,779/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,349万
-$24,550/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,143万
-$21,765/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,136万
-$21,761/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,239万
-$23,926/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,188万
-$25,339/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,278万
-$23,800/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,421万
-$27,074/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,404万
-$26,906/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,253万
-$24,076/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,195万
-$25,473/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,292万
-$23,950/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,400万
-$26,675/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,384万
-$26,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,183万
-$23,325/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,131万
-$24,123/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,263万
-$23,650/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,356万
-$25,831/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,172万
-$22,452/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,155万
-$23,025/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,109万
-$23,649/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,235万
-$23,350/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,045万
-$19,909/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,162万
-$22,258/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,169万
-$23,175/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,087万
-$23,186/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2,220万
-$23,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,275万
-$24,279/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1,304万
-$24,979/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 936呎 (3房)
-$2,174万
-$23,225/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1,085万
-$23,132/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,422万
-$26,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-$1,170万
-$24,281/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 479呎 (2房)
-$1,186万
-$24,768/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 894呎 (3房)
-$2,771万
-$31,000/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 431呎 (2房)
-$1,183万
-$27,437/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +156,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +237,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +673,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21415,4 +21614,4969 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>MAISON A</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>MAISON B</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>MAISON C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1564呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1564呎 (4+房)
+$7273万
+$46,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3533万
+$36,500/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$2075万
+$35,105/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$2075万
+$35,105/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$4034万
+$40,500/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3485万
+$36,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$2130万
+$36,045/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$2066万
+$34,964/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3984万
+$40,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$11280万
+$116,529/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$11280万
+$190,863/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$11280万
+$190,863/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$11280万
+$113,253/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3509万
+$36,250/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$2002万
+$33,871/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$2002万
+$33,871/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3884万
+$39,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3320万
+$34,298/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1970万
+$33,337/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1970万
+$33,337/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3830万
+$38,454/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3272万
+$33,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1939万
+$32,813/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1939万
+$32,813/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3795万
+$38,100/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3223万
+$33,300/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1909万
+$36,356/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1909万
+$32,296/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3792万
+$38,071/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3293万
+$34,021/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1879万
+$31,788/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1879万
+$31,788/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3741万
+$37,563/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3533万
+$36,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1956万
+$33,093/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$2081万
+$35,212/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3175万
+$32,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1891万
+$31,995/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1891万
+$31,995/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3486万
+$35,000/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3078万
+$31,798/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1853万
+$31,346/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1853万
+$31,346/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3436万
+$34,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+      <c r="H17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$3030万
+$31,300/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1842万
+$31,159/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1842万
+$31,159/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3436万
+$34,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+      <c r="H18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2981万
+$30,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1832万
+$31,004/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1832万
+$31,004/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3406万
+$34,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+      <c r="H19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2933万
+$30,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1934万
+$32,726/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1866万
+$31,576/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3685万
+$37,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+      <c r="H20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2885万
+$29,800/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1924万
+$32,563/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1814万
+$30,696/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+$3546万
+$35,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
+      <c r="H21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2885万
+$29,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1906万
+$32,242/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1796万
+$30,393/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr"/>
+      <c r="H22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2875万
+$29,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1817万
+$30,748/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1747万
+$29,564/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr"/>
+      <c r="H23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2768万
+$28,600/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1685万
+$28,505/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1685万
+$28,505/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr"/>
+      <c r="H24" s="21" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2860万
+$29,550/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1663万
+$28,141/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr"/>
+      <c r="H25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+$2681万
+$27,700/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1671万
+$28,279/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1623万
+$27,454/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr"/>
+      <c r="G26" s="21" t="inlineStr"/>
+      <c r="H26" s="21" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1583万
+$26,784/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr"/>
+      <c r="G27" s="21" t="inlineStr"/>
+      <c r="H27" s="21" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 968呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 591呎 (2房)
+$1583万
+$26,785/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1537万
+$26,005/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 996呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr"/>
+      <c r="G28" s="21" t="inlineStr"/>
+      <c r="H28" s="21" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 925呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 548呎 (2房)
+$1660万
+$30,292/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 548呎 (2房)
+$1708万
+$31,168/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 953呎 (3房)
+$3383万
+$35,500/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr"/>
+      <c r="G29" s="21" t="inlineStr"/>
+      <c r="H29" s="21" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr"/>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>MAISON A | 1108呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>MAISON B | 967呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>MAISON C | 967呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$835万
+$25,061/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$839万
+$24,820/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1460万
+$26,995/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$987万
+$27,116/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 959呎 (3房)
+$2976万
+$31,032/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$775万
+$23,260/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$779万
+$23,058/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1373万
+$25,380/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$893万
+$24,524/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3201万
+$33,348/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$770万
+$23,119/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$775万
+$22,918/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1360万
+$25,130/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$765万
+$21,026/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 959呎 (3房)
+$2880万
+$30,031/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$768万
+$23,048/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$772万
+$22,851/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1394万
+$25,769/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$887万
+$24,377/呎
+(23年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2832万
+$29,500/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$765万
+$22,980/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$770万
+$22,782/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1333万
+$24,635/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$895万
+$24,590/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3098万
+$32,266/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$763万
+$22,912/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$768万
+$22,715/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1320万
+$24,391/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$913万
+$25,085/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2736万
+$28,500/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$761万
+$22,841/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$765万
+$22,645/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1307万
+$24,150/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 365呎 (1房)
+$910万
+$24,941/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2771万
+$28,866/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$758万
+$22,776/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$763万
+$22,578/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1294万
+$23,911/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$908万
+$24,937/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2659万
+$27,700/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$764万
+$22,942/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 943呎 (1房)
+$761万
+$8,069/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1281万
+$23,674/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$905万
+$24,862/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2707万
+$28,196/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$762万
+$22,871/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$759万
+$22,441/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1253万
+$23,160/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$872万
+$23,942/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2592万
+$27,000/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$757万
+$22,742/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$759万
+$22,441/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1253万
+$23,160/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$902万
+$24,787/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3058万
+$31,854/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$749万
+$22,503/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$754万
+$22,309/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1228万
+$22,700/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 365呎 (1房)
+$897万
+$24,570/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2544万
+$26,500/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$747万
+$22,438/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$752万
+$22,240/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1209万
+$22,355/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$894万
+$24,567/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2515万
+$26,200/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$745万
+$22,370/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$749万
+$22,173/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1191万
+$22,014/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$861万
+$23,657/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 959呎 (3房)
+$2486万
+$25,927/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$746万
+$22,400/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$747万
+$22,108/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1173万
+$21,674/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$888万
+$24,396/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2477万
+$25,800/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$740万
+$22,236/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$745万
+$22,044/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1169万
+$21,609/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$854万
+$23,468/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2867万
+$29,862/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$738万
+$22,170/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$743万
+$21,977/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1166万
+$21,543/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$880万
+$24,176/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2924万
+$30,459/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$736万
+$22,102/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$741万
+$21,909/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1147万
+$21,208/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$738万
+$20,262/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2764万
+$28,788/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$741万
+$22,266/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$750万
+$22,199/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1147万
+$21,208/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$863万
+$23,702/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2256万
+$23,500/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$737万
+$22,129/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$736万
+$21,780/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1144万
+$21,144/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$859万
+$23,586/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2208万
+$23,000/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$737万
+$22,130/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$734万
+$21,713/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1126万
+$20,811/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$730万
+$20,059/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2131万
+$22,200/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$727万
+$21,840/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$732万
+$21,649/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1086万
+$20,074/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$727万
+$19,961/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2504万
+$26,081/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$720万
+$21,623/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$721万
+$21,323/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1046万
+$19,342/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$809万
+$22,221/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2064万
+$21,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$721万
+$21,639/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$711万
+$21,040/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1022万
+$18,888/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$799万
+$21,948/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 916呎 (3房)
+$2843万
+$31,034/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 311呎 (1房)
+$787万
+$25,308/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 317呎 (1房)
+$805万
+$25,403/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 504呎 (2房)
+$1143万
+$22,688/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 327呎 (1房)
+$863万
+$26,400/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>MAISON D</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>MAISON E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>A | 1615呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>B | 1556呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1615呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1556呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3639万
+$36,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2138万
+$35,807/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2152万
+$36,046/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2154万
+$36,089/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2022万
+$33,871/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2374万
+$40,039/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3420万
+$34,301/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1990万
+$33,337/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1959万
+$32,814/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1967万
+$32,942/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1947万
+$32,832/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1898万
+$31,789/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1928万
+$32,295/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3210万
+$32,201/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1883万
+$31,536/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2215万
+$37,352/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3170万
+$31,800/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1871万
+$31,347/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2202万
+$37,130/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3121万
+$31,300/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1876万
+$31,419/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3071万
+$30,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1851万
+$31,005/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3021万
+$30,301/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1923万
+$32,205/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1907万
+$32,156/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$2971万
+$29,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1869万
+$31,310/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1833万
+$30,905/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$2921万
+$29,301/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1836万
+$30,960/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1765万
+$29,564/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1786万
+$30,117/呎
+(24年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1789万
+$29,964/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1680万
+$28,141/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1723万
+$29,047/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1657万
+$27,762/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr"/>
+      <c r="G26" s="21" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1581万
+$26,487/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1624万
+$27,381/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr"/>
+      <c r="G27" s="21" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1589万
+$26,622/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1576万
+$26,584/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr"/>
+      <c r="G28" s="21" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 954呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 555呎 (2房)
+$1988万
+$35,823/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1957万
+$35,589/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 949呎 (3房)
+$3421万
+$36,048/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr"/>
+      <c r="G29" s="21" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr"/>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>MAISON D | 889呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>MAISON E | 940呎 (3房)
+$2880万
+$30,638/呎
+(23年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1144呎 (3房)
+$4777万
+$41,757/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 425呎 (2房)
+$1384万
+$32,572/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 425呎 (2房)
+$1357万
+$31,928/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 1116呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1314万
+$28,006/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1399万
+$26,654/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1483万
+$28,407/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$3064万
+$32,735/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1270万
+$27,077/呎
+(23年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1437万
+$27,377/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1454万
+$27,850/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$3017万
+$32,234/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1124万
+$23,955/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$3067万
+$32,050/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1345万
+$25,621/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1425万
+$27,303/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2970万
+$31,734/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1117万
+$23,812/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1319万
+$25,118/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1410万
+$27,008/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2783万
+$29,732/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1110万
+$23,669/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2828万
+$29,550/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1293万
+$24,626/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1385万
+$26,537/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2736万
+$29,231/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1104万
+$23,529/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2780万
+$29,050/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1283万
+$24,430/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1374万
+$26,327/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2689万
+$28,731/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1247万
+$26,587/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$3030万
+$31,659/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1587万
+$30,232/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1363万
+$26,118/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2642万
+$28,230/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1268万
+$27,042/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2909万
+$30,397/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1247万
+$23,755/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1240万
+$23,752/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2595万
+$27,729/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1090万
+$23,238/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2994万
+$31,283/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1237万
+$23,566/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1491万
+$28,563/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 937呎 (3房)
+$2549万
+$27,200/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1253万
+$26,721/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2589万
+$27,050/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1237万
+$23,566/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1230万
+$23,565/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 937呎 (3房)
+$2502万
+$26,700/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1232万
+$26,265/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2560万
+$26,750/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1225万
+$23,333/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1218万
+$23,332/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2474万
+$26,427/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1203万
+$25,656/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2874万
+$30,030/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1219万
+$23,216/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1212万
+$23,214/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2441万
+$26,078/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1242万
+$26,481/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2923万
+$30,544/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1213万
+$23,101/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1206万
+$23,098/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2417万
+$25,827/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1238万
+$26,402/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2474万
+$25,850/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1250万
+$23,806/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1257万
+$24,079/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2389万
+$25,527/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1231万
+$26,244/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2445万
+$25,550/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1490万
+$28,383/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1230万
+$23,562/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 937呎 (3房)
+$2361万
+$25,200/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1224万
+$26,088/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2383万
+$24,900/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1177万
+$22,422/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1170万
+$22,421/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 937呎 (3房)
+$2314万
+$24,700/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1196万
+$25,491/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2378万
+$24,850/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1201万
+$22,880/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1153万
+$22,088/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 937呎 (3房)
+$2268万
+$24,200/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1209万
+$25,779/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2349万
+$24,550/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1143万
+$21,765/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1136万
+$21,761/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2239万
+$23,926/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1188万
+$25,339/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2278万
+$23,800/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1421万
+$27,074/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1404万
+$26,906/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2253万
+$24,076/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1195万
+$25,473/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2292万
+$23,950/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1400万
+$26,675/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1384万
+$26,508/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2183万
+$23,325/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1131万
+$24,123/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2263万
+$23,650/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1356万
+$25,831/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1172万
+$22,452/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2155万
+$23,025/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1109万
+$23,649/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2235万
+$23,350/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1045万
+$19,909/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1162万
+$22,258/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2169万
+$23,175/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1087万
+$23,186/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2220万
+$23,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1275万
+$24,279/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1304万
+$24,979/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 936呎 (3房)
+$2174万
+$23,225/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1085万
+$23,132/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2422万
+$26,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+$1170万
+$24,281/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 479呎 (2房)
+$1186万
+$24,768/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 894呎 (3房)
+$2771万
+$31,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 431呎 (2房)
+$1183万
+$27,437/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -673,7 +673,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -678,7 +678,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>上車置優越 360天付款計劃</t>
+          <t>如「瑜」得水 120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>上車置優越 360天付款計劃</t>
+          <t>如「瑜」得水 120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>上車置優越 360天付款計劃</t>
+          <t>如「瑜」得水 120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
@@ -21036,7 +21036,7 @@
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>上車置優越 360天付款計劃</t>
+          <t>如「瑜」得水 120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
-          <t>上車置優越 360天付款計劃</t>
+          <t>如「瑜」得水 120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N321" s="3" t="inlineStr">

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -19026,7 +19026,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -29279,7 +29279,7 @@
           <t>B | 1564呎 (4+房)
 $7273万
 $46,500/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -29299,7 +29299,7 @@
           <t>A | 968呎 (3房)
 $3533万
 $36,500/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -29307,7 +29307,7 @@
           <t>B | 591呎 (2房)
 $2075万
 $35,105/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>C | 591呎 (2房)
 $2075万
 $35,105/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>D | 996呎 (3房)
 $4034万
 $40,500/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -29341,7 +29341,7 @@
           <t>A | 968呎 (3房)
 $3485万
 $36,000/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -29349,7 +29349,7 @@
           <t>B | 591呎 (2房)
 $2130万
 $36,045/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -29357,7 +29357,7 @@
           <t>C | 591呎 (2房)
 $2066万
 $34,964/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -29365,7 +29365,7 @@
           <t>D | 996呎 (3房)
 $3984万
 $40,000/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -29383,7 +29383,7 @@
           <t>A | 968呎 (3房)
 $11280万
 $116,529/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -29391,7 +29391,7 @@
           <t>B | 591呎 (2房)
 $11280万
 $190,863/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -29399,7 +29399,7 @@
           <t>C | 591呎 (2房)
 $11280万
 $190,863/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -29407,7 +29407,7 @@
           <t>D | 996呎 (3房)
 $11280万
 $113,253/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -29425,7 +29425,7 @@
           <t>A | 968呎 (3房)
 $3509万
 $36,250/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -29433,7 +29433,7 @@
           <t>B | 591呎 (2房)
 $2002万
 $33,871/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -29441,7 +29441,7 @@
           <t>C | 591呎 (2房)
 $2002万
 $33,871/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -29449,7 +29449,7 @@
           <t>D | 996呎 (3房)
 $3884万
 $39,000/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -29467,7 +29467,7 @@
           <t>A | 968呎 (3房)
 $3320万
 $34,298/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -29475,7 +29475,7 @@
           <t>B | 591呎 (2房)
 $1970万
 $33,337/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -29483,7 +29483,7 @@
           <t>C | 591呎 (2房)
 $1970万
 $33,337/呎
-(25年-07月-29日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -29491,7 +29491,7 @@
           <t>D | 996呎 (3房)
 $3830万
 $38,454/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -29509,7 +29509,7 @@
           <t>A | 968呎 (3房)
 $3272万
 $33,800/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -29517,7 +29517,7 @@
           <t>B | 591呎 (2房)
 $1939万
 $32,813/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -29525,7 +29525,7 @@
           <t>C | 591呎 (2房)
 $1939万
 $32,813/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -29533,7 +29533,7 @@
           <t>D | 996呎 (3房)
 $3795万
 $38,100/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
           <t>A | 968呎 (3房)
 $3223万
 $33,300/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -29559,7 +29559,7 @@
           <t>B | 525呎 (2房)
 $1909万
 $36,356/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -29567,7 +29567,7 @@
           <t>C | 591呎 (2房)
 $1909万
 $32,296/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -29575,7 +29575,7 @@
           <t>D | 996呎 (3房)
 $3792万
 $38,071/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -29593,7 +29593,7 @@
           <t>A | 968呎 (3房)
 $3293万
 $34,021/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -29601,7 +29601,7 @@
           <t>B | 591呎 (2房)
 $1879万
 $31,788/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -29609,7 +29609,7 @@
           <t>C | 591呎 (2房)
 $1879万
 $31,788/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -29617,7 +29617,7 @@
           <t>D | 996呎 (3房)
 $3741万
 $37,563/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -29635,7 +29635,7 @@
           <t>A | 968呎 (3房)
 $3533万
 $36,500/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -29643,7 +29643,7 @@
           <t>B | 591呎 (2房)
 $1956万
 $33,093/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -29651,7 +29651,7 @@
           <t>C | 591呎 (2房)
 $2081万
 $35,212/呎
-(25年-08月-06日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -29677,7 +29677,7 @@
           <t>A | 968呎 (3房)
 $3175万
 $32,800/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -29685,7 +29685,7 @@
           <t>B | 591呎 (2房)
 $1891万
 $31,995/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -29693,7 +29693,7 @@
           <t>C | 591呎 (2房)
 $1891万
 $31,995/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -29701,7 +29701,7 @@
           <t>D | 996呎 (3房)
 $3486万
 $35,000/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -29719,7 +29719,7 @@
           <t>A | 968呎 (3房)
 $3078万
 $31,798/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -29727,7 +29727,7 @@
           <t>B | 591呎 (2房)
 $1853万
 $31,346/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -29735,7 +29735,7 @@
           <t>C | 591呎 (2房)
 $1853万
 $31,346/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -29743,7 +29743,7 @@
           <t>D | 996呎 (3房)
 $3436万
 $34,500/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -29761,7 +29761,7 @@
           <t>A | 968呎 (3房)
 $3030万
 $31,300/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -29769,7 +29769,7 @@
           <t>B | 591呎 (2房)
 $1842万
 $31,159/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -29777,7 +29777,7 @@
           <t>C | 591呎 (2房)
 $1842万
 $31,159/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -29785,7 +29785,7 @@
           <t>D | 996呎 (3房)
 $3436万
 $34,500/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -29803,7 +29803,7 @@
           <t>A | 968呎 (3房)
 $2981万
 $30,800/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -29811,7 +29811,7 @@
           <t>B | 591呎 (2房)
 $1832万
 $31,004/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -29819,7 +29819,7 @@
           <t>C | 591呎 (2房)
 $1832万
 $31,004/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -29827,7 +29827,7 @@
           <t>D | 996呎 (3房)
 $3406万
 $34,200/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
           <t>A | 968呎 (3房)
 $2933万
 $30,300/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -29853,7 +29853,7 @@
           <t>B | 591呎 (2房)
 $1934万
 $32,726/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29861,7 +29861,7 @@
           <t>C | 591呎 (2房)
 $1866万
 $31,576/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -29869,7 +29869,7 @@
           <t>D | 996呎 (3房)
 $3685万
 $37,000/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -29887,7 +29887,7 @@
           <t>A | 968呎 (3房)
 $2885万
 $29,800/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -29895,7 +29895,7 @@
           <t>B | 591呎 (2房)
 $1924万
 $32,563/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -29903,7 +29903,7 @@
           <t>C | 591呎 (2房)
 $1814万
 $30,696/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -29911,7 +29911,7 @@
           <t>D | 996呎 (3房)
 $3546万
 $35,600/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
           <t>A | 968呎 (3房)
 $2885万
 $29,800/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -29937,7 +29937,7 @@
           <t>B | 591呎 (2房)
 $1906万
 $32,242/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29945,7 +29945,7 @@
           <t>C | 591呎 (2房)
 $1796万
 $30,393/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -29971,7 +29971,7 @@
           <t>A | 968呎 (3房)
 $2875万
 $29,700/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29979,7 +29979,7 @@
           <t>B | 591呎 (2房)
 $1817万
 $30,748/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -29987,7 +29987,7 @@
           <t>C | 591呎 (2房)
 $1747万
 $29,564/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -30013,7 +30013,7 @@
           <t>A | 968呎 (3房)
 $2768万
 $28,600/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -30021,7 +30021,7 @@
           <t>B | 591呎 (2房)
 $1685万
 $28,505/呎
-(25年-05月-15日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -30029,7 +30029,7 @@
           <t>C | 591呎 (2房)
 $1685万
 $28,505/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -30055,7 +30055,7 @@
           <t>A | 968呎 (3房)
 $2860万
 $29,550/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -30071,7 +30071,7 @@
           <t>C | 591呎 (2房)
 $1663万
 $28,141/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -30097,7 +30097,7 @@
           <t>A | 968呎 (3房)
 $2681万
 $27,700/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -30105,7 +30105,7 @@
           <t>B | 591呎 (2房)
 $1671万
 $28,279/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -30113,7 +30113,7 @@
           <t>C | 591呎 (2房)
 $1623万
 $27,454/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -30155,7 +30155,7 @@
           <t>C | 591呎 (2房)
 $1583万
 $26,784/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -30189,7 +30189,7 @@
           <t>B | 591呎 (2房)
 $1583万
 $26,785/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -30197,7 +30197,7 @@
           <t>C | 591呎 (2房)
 $1537万
 $26,005/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -30231,7 +30231,7 @@
           <t>B | 548呎 (2房)
 $1660万
 $30,292/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -30239,7 +30239,7 @@
           <t>C | 548呎 (2房)
 $1708万
 $31,168/呎
-(25年-05月-28日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -30247,7 +30247,7 @@
           <t>D | 953呎 (3房)
 $3383万
 $35,500/呎
-(23年-07月-04日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
@@ -30437,7 +30437,7 @@
           <t>B | 333呎 (1房)
 $835万
 $25,061/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -30445,7 +30445,7 @@
           <t>C | 338呎 (1房)
 $839万
 $24,820/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -30453,7 +30453,7 @@
           <t>D | 541呎 (2房)
 $1460万
 $26,995/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -30461,7 +30461,7 @@
           <t>E | 364呎 (1房)
 $987万
 $27,116/呎
-(23年-12月-20日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -30476,7 +30476,7 @@
           <t>A | 959呎 (3房)
 $2976万
 $31,032/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30484,7 +30484,7 @@
           <t>B | 333呎 (1房)
 $775万
 $23,260/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -30492,7 +30492,7 @@
           <t>C | 338呎 (1房)
 $779万
 $23,058/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -30500,7 +30500,7 @@
           <t>D | 541呎 (2房)
 $1373万
 $25,380/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -30508,7 +30508,7 @@
           <t>E | 364呎 (1房)
 $893万
 $24,524/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30523,7 +30523,7 @@
           <t>A | 960呎 (3房)
 $3201万
 $33,348/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30531,7 +30531,7 @@
           <t>B | 333呎 (1房)
 $770万
 $23,119/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -30539,7 +30539,7 @@
           <t>C | 338呎 (1房)
 $775万
 $22,918/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -30547,7 +30547,7 @@
           <t>D | 541呎 (2房)
 $1360万
 $25,130/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -30555,7 +30555,7 @@
           <t>E | 364呎 (1房)
 $765万
 $21,026/呎
-(25年-05月-22日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -30570,7 +30570,7 @@
           <t>A | 959呎 (3房)
 $2880万
 $30,031/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -30578,7 +30578,7 @@
           <t>B | 333呎 (1房)
 $768万
 $23,048/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -30586,7 +30586,7 @@
           <t>C | 338呎 (1房)
 $772万
 $22,851/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -30594,7 +30594,7 @@
           <t>D | 541呎 (2房)
 $1394万
 $25,769/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -30602,7 +30602,7 @@
           <t>E | 364呎 (1房)
 $887万
 $24,377/呎
-(23年-09月-26日)</t>
+(23年-09月)</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
           <t>A | 960呎 (3房)
 $2832万
 $29,500/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30625,7 +30625,7 @@
           <t>B | 333呎 (1房)
 $765万
 $22,980/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -30633,7 +30633,7 @@
           <t>C | 338呎 (1房)
 $770万
 $22,782/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -30641,7 +30641,7 @@
           <t>D | 541呎 (2房)
 $1333万
 $24,635/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -30649,7 +30649,7 @@
           <t>E | 364呎 (1房)
 $895万
 $24,590/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30664,7 @@
           <t>A | 960呎 (3房)
 $3098万
 $32,266/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -30672,7 +30672,7 @@
           <t>B | 333呎 (1房)
 $763万
 $22,912/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -30680,7 +30680,7 @@
           <t>C | 338呎 (1房)
 $768万
 $22,715/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -30688,7 +30688,7 @@
           <t>D | 541呎 (2房)
 $1320万
 $24,391/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -30696,7 +30696,7 @@
           <t>E | 364呎 (1房)
 $913万
 $25,085/呎
-(23年-06月-08日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
           <t>A | 960呎 (3房)
 $2736万
 $28,500/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30719,7 +30719,7 @@
           <t>B | 333呎 (1房)
 $761万
 $22,841/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -30727,7 +30727,7 @@
           <t>C | 338呎 (1房)
 $765万
 $22,645/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -30735,7 +30735,7 @@
           <t>D | 541呎 (2房)
 $1307万
 $24,150/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -30743,7 +30743,7 @@
           <t>E | 365呎 (1房)
 $910万
 $24,941/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30758,7 +30758,7 @@
           <t>A | 960呎 (3房)
 $2771万
 $28,866/呎
-(25年-05月-18日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30766,7 +30766,7 @@
           <t>B | 333呎 (1房)
 $758万
 $22,776/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -30774,7 +30774,7 @@
           <t>C | 338呎 (1房)
 $763万
 $22,578/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -30782,7 +30782,7 @@
           <t>D | 541呎 (2房)
 $1294万
 $23,911/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -30790,7 +30790,7 @@
           <t>E | 364呎 (1房)
 $908万
 $24,937/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30805,7 +30805,7 @@
           <t>A | 960呎 (3房)
 $2659万
 $27,700/呎
-(25年-06月-01日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -30813,7 +30813,7 @@
           <t>B | 333呎 (1房)
 $764万
 $22,942/呎
-(24年-07月-15日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -30821,7 +30821,7 @@
           <t>C | 943呎 (1房)
 $761万
 $8,069/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -30829,7 +30829,7 @@
           <t>D | 541呎 (2房)
 $1281万
 $23,674/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -30837,7 +30837,7 @@
           <t>E | 364呎 (1房)
 $905万
 $24,862/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30852,7 +30852,7 @@
           <t>A | 960呎 (3房)
 $2707万
 $28,196/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -30860,7 +30860,7 @@
           <t>B | 333呎 (1房)
 $762万
 $22,871/呎
-(24年-07月-10日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -30868,7 +30868,7 @@
           <t>C | 338呎 (1房)
 $759万
 $22,441/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -30876,7 +30876,7 @@
           <t>D | 541呎 (2房)
 $1253万
 $23,160/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -30884,7 +30884,7 @@
           <t>E | 364呎 (1房)
 $872万
 $23,942/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30899,7 +30899,7 @@
           <t>A | 960呎 (3房)
 $2592万
 $27,000/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30907,7 +30907,7 @@
           <t>B | 333呎 (1房)
 $757万
 $22,742/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -30915,7 +30915,7 @@
           <t>C | 338呎 (1房)
 $759万
 $22,441/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -30923,7 +30923,7 @@
           <t>D | 541呎 (2房)
 $1253万
 $23,160/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -30931,7 +30931,7 @@
           <t>E | 364呎 (1房)
 $902万
 $24,787/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -30946,7 +30946,7 @@
           <t>A | 960呎 (3房)
 $3058万
 $31,854/呎
-(23年-08月-08日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -30954,7 +30954,7 @@
           <t>B | 333呎 (1房)
 $749万
 $22,503/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -30962,7 +30962,7 @@
           <t>C | 338呎 (1房)
 $754万
 $22,309/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -30970,7 +30970,7 @@
           <t>D | 541呎 (2房)
 $1228万
 $22,700/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -30978,7 +30978,7 @@
           <t>E | 365呎 (1房)
 $897万
 $24,570/呎
-(23年-07月-11日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -30993,7 +30993,7 @@
           <t>A | 960呎 (3房)
 $2544万
 $26,500/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -31001,7 +31001,7 @@
           <t>B | 333呎 (1房)
 $747万
 $22,438/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -31009,7 +31009,7 @@
           <t>C | 338呎 (1房)
 $752万
 $22,240/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -31017,7 +31017,7 @@
           <t>D | 541呎 (2房)
 $1209万
 $22,355/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -31025,7 +31025,7 @@
           <t>E | 364呎 (1房)
 $894万
 $24,567/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
           <t>A | 960呎 (3房)
 $2515万
 $26,200/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -31048,7 +31048,7 @@
           <t>B | 333呎 (1房)
 $745万
 $22,370/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -31056,7 +31056,7 @@
           <t>C | 338呎 (1房)
 $749万
 $22,173/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -31064,7 +31064,7 @@
           <t>D | 541呎 (2房)
 $1191万
 $22,014/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -31072,7 +31072,7 @@
           <t>E | 364呎 (1房)
 $861万
 $23,657/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -31087,7 +31087,7 @@
           <t>A | 959呎 (3房)
 $2486万
 $25,927/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>B | 333呎 (1房)
 $746万
 $22,400/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -31103,7 +31103,7 @@
           <t>C | 338呎 (1房)
 $747万
 $22,108/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -31111,7 +31111,7 @@
           <t>D | 541呎 (2房)
 $1173万
 $21,674/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -31119,7 +31119,7 @@
           <t>E | 364呎 (1房)
 $888万
 $24,396/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31134,7 @@
           <t>A | 960呎 (3房)
 $2477万
 $25,800/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -31142,7 +31142,7 @@
           <t>B | 333呎 (1房)
 $740万
 $22,236/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -31150,7 +31150,7 @@
           <t>C | 338呎 (1房)
 $745万
 $22,044/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -31158,7 +31158,7 @@
           <t>D | 541呎 (2房)
 $1169万
 $21,609/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -31166,7 +31166,7 @@
           <t>E | 364呎 (1房)
 $854万
 $23,468/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31181,7 @@
           <t>A | 960呎 (3房)
 $2867万
 $29,862/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -31189,7 +31189,7 @@
           <t>B | 333呎 (1房)
 $738万
 $22,170/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -31197,7 +31197,7 @@
           <t>C | 338呎 (1房)
 $743万
 $21,977/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -31205,7 +31205,7 @@
           <t>D | 541呎 (2房)
 $1166万
 $21,543/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -31213,7 +31213,7 @@
           <t>E | 364呎 (1房)
 $880万
 $24,176/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -31228,7 +31228,7 @@
           <t>A | 960呎 (3房)
 $2924万
 $30,459/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -31236,7 +31236,7 @@
           <t>B | 333呎 (1房)
 $736万
 $22,102/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -31244,7 +31244,7 @@
           <t>C | 338呎 (1房)
 $741万
 $21,909/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -31252,7 +31252,7 @@
           <t>D | 541呎 (2房)
 $1147万
 $21,208/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -31260,7 +31260,7 @@
           <t>E | 364呎 (1房)
 $738万
 $20,262/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -31275,7 +31275,7 @@
           <t>A | 960呎 (3房)
 $2764万
 $28,788/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>B | 333呎 (1房)
 $741万
 $22,266/呎
-(24年-07月-15日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>C | 338呎 (1房)
 $750万
 $22,199/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>D | 541呎 (2房)
 $1147万
 $21,208/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -31307,7 +31307,7 @@
           <t>E | 364呎 (1房)
 $863万
 $23,702/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
           <t>A | 960呎 (3房)
 $2256万
 $23,500/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -31330,7 +31330,7 @@
           <t>B | 333呎 (1房)
 $737万
 $22,129/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>C | 338呎 (1房)
 $736万
 $21,780/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>D | 541呎 (2房)
 $1144万
 $21,144/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>E | 364呎 (1房)
 $859万
 $23,586/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -31369,7 +31369,7 @@
           <t>A | 960呎 (3房)
 $2208万
 $23,000/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -31377,7 +31377,7 @@
           <t>B | 333呎 (1房)
 $737万
 $22,130/呎
-(24年-07月-09日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -31385,7 +31385,7 @@
           <t>C | 338呎 (1房)
 $734万
 $21,713/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -31393,7 +31393,7 @@
           <t>D | 541呎 (2房)
 $1126万
 $20,811/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -31401,7 +31401,7 @@
           <t>E | 364呎 (1房)
 $730万
 $20,059/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -31416,7 +31416,7 @@
           <t>A | 960呎 (3房)
 $2131万
 $22,200/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -31424,7 +31424,7 @@
           <t>B | 333呎 (1房)
 $727万
 $21,840/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -31432,7 +31432,7 @@
           <t>C | 338呎 (1房)
 $732万
 $21,649/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -31440,7 +31440,7 @@
           <t>D | 541呎 (2房)
 $1086万
 $20,074/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -31448,7 +31448,7 @@
           <t>E | 364呎 (1房)
 $727万
 $19,961/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -31463,7 +31463,7 @@
           <t>A | 960呎 (3房)
 $2504万
 $26,081/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -31471,7 +31471,7 @@
           <t>B | 333呎 (1房)
 $720万
 $21,623/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -31479,7 +31479,7 @@
           <t>C | 338呎 (1房)
 $721万
 $21,323/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -31487,7 +31487,7 @@
           <t>D | 541呎 (2房)
 $1046万
 $19,342/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -31495,7 +31495,7 @@
           <t>E | 364呎 (1房)
 $809万
 $22,221/呎
-(24年-06月-10日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
           <t>A | 960呎 (3房)
 $2064万
 $21,500/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -31518,7 +31518,7 @@
           <t>B | 333呎 (1房)
 $721万
 $21,639/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -31526,7 +31526,7 @@
           <t>C | 338呎 (1房)
 $711万
 $21,040/呎
-(25年-05月-06日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -31534,7 +31534,7 @@
           <t>D | 541呎 (2房)
 $1022万
 $18,888/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -31542,7 +31542,7 @@
           <t>E | 364呎 (1房)
 $799万
 $21,948/呎
-(24年-03月-11日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -31557,7 +31557,7 @@
           <t>A | 916呎 (3房)
 $2843万
 $31,034/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -31565,7 +31565,7 @@
           <t>B | 311呎 (1房)
 $787万
 $25,308/呎
-(24年-07月-30日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -31573,7 +31573,7 @@
           <t>C | 317呎 (1房)
 $805万
 $25,403/呎
-(24年-08月-28日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -31581,7 +31581,7 @@
           <t>D | 504呎 (2房)
 $1143万
 $22,688/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -31589,7 +31589,7 @@
           <t>E | 327呎 (1房)
 $863万
 $26,400/呎
-(23年-06月-20日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -31793,7 +31793,7 @@
           <t>A | 997呎 (3房)
 $3639万
 $36,500/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -31801,7 +31801,7 @@
           <t>B | 597呎 (2房)
 $2138万
 $35,807/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
@@ -31842,7 +31842,7 @@
           <t>B | 597呎 (2房)
 $2152万
 $36,046/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -31883,7 +31883,7 @@
           <t>B | 597呎 (2房)
 $2154万
 $36,089/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -31924,7 +31924,7 @@
           <t>B | 597呎 (2房)
 $2022万
 $33,871/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -31957,7 +31957,7 @@
           <t>A | 997呎 (3房)
 $3420万
 $34,301/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -31965,7 +31965,7 @@
           <t>B | 597呎 (2房)
 $1990万
 $33,337/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -32006,7 +32006,7 @@
           <t>B | 597呎 (2房)
 $1959万
 $32,814/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -32047,7 +32047,7 @@
           <t>B | 597呎 (2房)
 $1967万
 $32,942/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -32055,7 +32055,7 @@
           <t>C | 593呎 (2房)
 $1947万
 $32,832/呎
-(23年-12月-06日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -32088,7 +32088,7 @@
           <t>B | 597呎 (2房)
 $1898万
 $31,789/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -32129,7 +32129,7 @@
           <t>B | 597呎 (2房)
 $1928万
 $32,295/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -32162,7 +32162,7 @@
           <t>A | 997呎 (3房)
 $3210万
 $32,201/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -32170,7 +32170,7 @@
           <t>B | 597呎 (2房)
 $1883万
 $31,536/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
@@ -32203,7 +32203,7 @@
           <t>A | 997呎 (3房)
 $3170万
 $31,800/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -32211,7 +32211,7 @@
           <t>B | 597呎 (2房)
 $1871万
 $31,347/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
@@ -32244,7 +32244,7 @@
           <t>A | 997呎 (3房)
 $3121万
 $31,300/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -32252,7 +32252,7 @@
           <t>B | 597呎 (2房)
 $1876万
 $31,419/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -32285,7 +32285,7 @@
           <t>A | 997呎 (3房)
 $3071万
 $30,800/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -32293,7 +32293,7 @@
           <t>B | 597呎 (2房)
 $1851万
 $31,005/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -32326,7 +32326,7 @@
           <t>A | 997呎 (3房)
 $3021万
 $30,301/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -32334,7 +32334,7 @@
           <t>B | 597呎 (2房)
 $1923万
 $32,205/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -32342,7 +32342,7 @@
           <t>C | 593呎 (2房)
 $1907万
 $32,156/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -32367,7 +32367,7 @@
           <t>A | 997呎 (3房)
 $2971万
 $29,800/呎
-(26年-06月-25日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -32375,7 +32375,7 @@
           <t>B | 597呎 (2房)
 $1869万
 $31,310/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -32383,7 +32383,7 @@
           <t>C | 593呎 (2房)
 $1833万
 $30,905/呎
-(23年-07月-03日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -32408,7 +32408,7 @@
           <t>A | 997呎 (3房)
 $2921万
 $29,301/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -32424,7 +32424,7 @@
           <t>C | 593呎 (2房)
 $1836万
 $30,960/呎
-(23年-11月-12日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -32457,7 +32457,7 @@
           <t>B | 597呎 (2房)
 $1765万
 $29,564/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -32465,7 +32465,7 @@
           <t>C | 593呎 (2房)
 $1786万
 $30,117/呎
-(24年-02月-06日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -32498,7 +32498,7 @@
           <t>B | 597呎 (2房)
 $1789万
 $29,964/呎
-(23年-06月-26日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -32539,7 +32539,7 @@
           <t>B | 597呎 (2房)
 $1680万
 $28,141/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -32547,7 +32547,7 @@
           <t>C | 593呎 (2房)
 $1723万
 $29,047/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -32580,7 +32580,7 @@
           <t>B | 597呎 (2房)
 $1657万
 $27,762/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -32621,7 +32621,7 @@
           <t>B | 597呎 (2房)
 $1581万
 $26,487/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -32629,7 +32629,7 @@
           <t>C | 593呎 (2房)
 $1624万
 $27,381/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -32662,7 +32662,7 @@
           <t>B | 597呎 (2房)
 $1589万
 $26,622/呎
-(23年-07月-03日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -32670,7 +32670,7 @@
           <t>C | 593呎 (2房)
 $1576万
 $26,584/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -32719,7 +32719,7 @@
           <t>D | 949呎 (3房)
 $3421万
 $36,048/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
@@ -32748,7 +32748,7 @@
           <t>MAISON E | 940呎 (3房)
 $2880万
 $30,638/呎
-(23年-11月-13日)</t>
+(23年-11月)</t>
         </is>
       </c>
     </row>
@@ -32892,7 +32892,7 @@
           <t>A | 1144呎 (3房)
 $4777万
 $41,757/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -32900,7 +32900,7 @@
           <t>B | 425呎 (2房)
 $1384万
 $32,572/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -32908,7 +32908,7 @@
           <t>C | 425呎 (2房)
 $1357万
 $31,928/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -32924,7 +32924,7 @@
           <t>E | 469呎 (2房)
 $1314万
 $28,006/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -32947,7 +32947,7 @@
           <t>B | 525呎 (2房)
 $1399万
 $26,654/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -32955,7 +32955,7 @@
           <t>C | 522呎 (2房)
 $1483万
 $28,407/呎
-(25年-06月-05日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -32963,7 +32963,7 @@
           <t>D | 936呎 (3房)
 $3064万
 $32,735/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -32971,7 +32971,7 @@
           <t>E | 469呎 (2房)
 $1270万
 $27,077/呎
-(23年-11月-02日)</t>
+(23年-11月)</t>
         </is>
       </c>
     </row>
@@ -32994,7 +32994,7 @@
           <t>B | 525呎 (2房)
 $1437万
 $27,377/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -33002,7 +33002,7 @@
           <t>C | 522呎 (2房)
 $1454万
 $27,850/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -33010,7 +33010,7 @@
           <t>D | 936呎 (3房)
 $3017万
 $32,234/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -33018,7 +33018,7 @@
           <t>E | 469呎 (2房)
 $1124万
 $23,955/呎
-(25年-05月-22日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33033,7 @@
           <t>A | 957呎 (3房)
 $3067万
 $32,050/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -33041,7 +33041,7 @@
           <t>B | 525呎 (2房)
 $1345万
 $25,621/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -33049,7 +33049,7 @@
           <t>C | 522呎 (2房)
 $1425万
 $27,303/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -33057,7 +33057,7 @@
           <t>D | 936呎 (3房)
 $2970万
 $31,734/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -33065,7 +33065,7 @@
           <t>E | 469呎 (2房)
 $1117万
 $23,812/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -33088,7 +33088,7 @@
           <t>B | 525呎 (2房)
 $1319万
 $25,118/呎
-(25年-05月-18日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -33096,7 +33096,7 @@
           <t>C | 522呎 (2房)
 $1410万
 $27,008/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -33104,7 +33104,7 @@
           <t>D | 936呎 (3房)
 $2783万
 $29,732/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -33112,7 +33112,7 @@
           <t>E | 469呎 (2房)
 $1110万
 $23,669/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
           <t>A | 957呎 (3房)
 $2828万
 $29,550/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -33135,7 +33135,7 @@
           <t>B | 525呎 (2房)
 $1293万
 $24,626/呎
-(25年-05月-11日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -33143,7 +33143,7 @@
           <t>C | 522呎 (2房)
 $1385万
 $26,537/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -33151,7 +33151,7 @@
           <t>D | 936呎 (3房)
 $2736万
 $29,231/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -33159,7 +33159,7 @@
           <t>E | 469呎 (2房)
 $1104万
 $23,529/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33174,7 @@
           <t>A | 957呎 (3房)
 $2780万
 $29,050/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -33182,7 +33182,7 @@
           <t>B | 525呎 (2房)
 $1283万
 $24,430/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -33190,7 +33190,7 @@
           <t>C | 522呎 (2房)
 $1374万
 $26,327/呎
-(25年-05月-28日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -33198,7 +33198,7 @@
           <t>D | 936呎 (3房)
 $2689万
 $28,731/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -33206,7 +33206,7 @@
           <t>E | 469呎 (2房)
 $1247万
 $26,587/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -33221,7 +33221,7 @@
           <t>A | 957呎 (3房)
 $3030万
 $31,659/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -33229,7 +33229,7 @@
           <t>B | 525呎 (2房)
 $1587万
 $30,232/呎
-(23年-12月-07日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -33237,7 +33237,7 @@
           <t>C | 522呎 (2房)
 $1363万
 $26,118/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -33245,7 +33245,7 @@
           <t>D | 936呎 (3房)
 $2642万
 $28,230/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -33253,7 +33253,7 @@
           <t>E | 469呎 (2房)
 $1268万
 $27,042/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33268,7 @@
           <t>A | 957呎 (3房)
 $2909万
 $30,397/呎
-(23年-06月-29日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -33276,7 +33276,7 @@
           <t>B | 525呎 (2房)
 $1247万
 $23,755/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -33284,7 +33284,7 @@
           <t>C | 522呎 (2房)
 $1240万
 $23,752/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -33292,7 +33292,7 @@
           <t>D | 936呎 (3房)
 $2595万
 $27,729/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -33300,7 +33300,7 @@
           <t>E | 469呎 (2房)
 $1090万
 $23,238/呎
-(25年-06月-05日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -33315,7 +33315,7 @@
           <t>A | 957呎 (3房)
 $2994万
 $31,283/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -33323,7 +33323,7 @@
           <t>B | 525呎 (2房)
 $1237万
 $23,566/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -33331,7 +33331,7 @@
           <t>C | 522呎 (2房)
 $1491万
 $28,563/呎
-(23年-09月-24日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -33339,7 +33339,7 @@
           <t>D | 937呎 (3房)
 $2549万
 $27,200/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -33347,7 +33347,7 @@
           <t>E | 469呎 (2房)
 $1253万
 $26,721/呎
-(23年-06月-19日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33362,7 +33362,7 @@
           <t>A | 957呎 (3房)
 $2589万
 $27,050/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -33370,7 +33370,7 @@
           <t>B | 525呎 (2房)
 $1237万
 $23,566/呎
-(25年-05月-11日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -33378,7 +33378,7 @@
           <t>C | 522呎 (2房)
 $1230万
 $23,565/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -33386,7 +33386,7 @@
           <t>D | 937呎 (3房)
 $2502万
 $26,700/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -33394,7 +33394,7 @@
           <t>E | 469呎 (2房)
 $1232万
 $26,265/呎
-(23年-06月-08日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33409,7 +33409,7 @@
           <t>A | 957呎 (3房)
 $2560万
 $26,750/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -33417,7 +33417,7 @@
           <t>B | 525呎 (2房)
 $1225万
 $23,333/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -33425,7 +33425,7 @@
           <t>C | 522呎 (2房)
 $1218万
 $23,332/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -33433,7 +33433,7 @@
           <t>D | 936呎 (3房)
 $2474万
 $26,427/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -33441,7 +33441,7 @@
           <t>E | 469呎 (2房)
 $1203万
 $25,656/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33456,7 @@
           <t>A | 957呎 (3房)
 $2874万
 $30,030/呎
-(23年-10月-08日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -33464,7 +33464,7 @@
           <t>B | 525呎 (2房)
 $1219万
 $23,216/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -33472,7 +33472,7 @@
           <t>C | 522呎 (2房)
 $1212万
 $23,214/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -33480,7 +33480,7 @@
           <t>D | 936呎 (3房)
 $2441万
 $26,078/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -33488,7 +33488,7 @@
           <t>E | 469呎 (2房)
 $1242万
 $26,481/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33503,7 +33503,7 @@
           <t>A | 957呎 (3房)
 $2923万
 $30,544/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -33511,7 +33511,7 @@
           <t>B | 525呎 (2房)
 $1213万
 $23,101/呎
-(25年-05月-15日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -33519,7 +33519,7 @@
           <t>C | 522呎 (2房)
 $1206万
 $23,098/呎
-(25年-05月-11日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -33527,7 +33527,7 @@
           <t>D | 936呎 (3房)
 $2417万
 $25,827/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -33535,7 +33535,7 @@
           <t>E | 469呎 (2房)
 $1238万
 $26,402/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33550,7 +33550,7 @@
           <t>A | 957呎 (3房)
 $2474万
 $25,850/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -33558,7 +33558,7 @@
           <t>B | 525呎 (2房)
 $1250万
 $23,806/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -33566,7 +33566,7 @@
           <t>C | 522呎 (2房)
 $1257万
 $24,079/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -33574,7 +33574,7 @@
           <t>D | 936呎 (3房)
 $2389万
 $25,527/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -33582,7 +33582,7 @@
           <t>E | 469呎 (2房)
 $1231万
 $26,244/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33597,7 +33597,7 @@
           <t>A | 957呎 (3房)
 $2445万
 $25,550/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -33605,7 +33605,7 @@
           <t>B | 525呎 (2房)
 $1490万
 $28,383/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -33613,7 +33613,7 @@
           <t>C | 522呎 (2房)
 $1230万
 $23,562/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -33621,7 +33621,7 @@
           <t>D | 937呎 (3房)
 $2361万
 $25,200/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -33629,7 +33629,7 @@
           <t>E | 469呎 (2房)
 $1224万
 $26,088/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33644,7 +33644,7 @@
           <t>A | 957呎 (3房)
 $2383万
 $24,900/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -33652,7 +33652,7 @@
           <t>B | 525呎 (2房)
 $1177万
 $22,422/呎
-(25年-05月-15日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -33660,7 +33660,7 @@
           <t>C | 522呎 (2房)
 $1170万
 $22,421/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -33668,7 +33668,7 @@
           <t>D | 937呎 (3房)
 $2314万
 $24,700/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -33676,7 +33676,7 @@
           <t>E | 469呎 (2房)
 $1196万
 $25,491/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33691,7 +33691,7 @@
           <t>A | 957呎 (3房)
 $2378万
 $24,850/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -33699,7 +33699,7 @@
           <t>B | 525呎 (2房)
 $1201万
 $22,880/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -33707,7 +33707,7 @@
           <t>C | 522呎 (2房)
 $1153万
 $22,088/呎
-(25年-05月-21日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -33715,7 +33715,7 @@
           <t>D | 937呎 (3房)
 $2268万
 $24,200/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -33723,7 +33723,7 @@
           <t>E | 469呎 (2房)
 $1209万
 $25,779/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33738,7 +33738,7 @@
           <t>A | 957呎 (3房)
 $2349万
 $24,550/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -33746,7 +33746,7 @@
           <t>B | 525呎 (2房)
 $1143万
 $21,765/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -33754,7 +33754,7 @@
           <t>C | 522呎 (2房)
 $1136万
 $21,761/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -33762,7 +33762,7 @@
           <t>D | 936呎 (3房)
 $2239万
 $23,926/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -33770,7 +33770,7 @@
           <t>E | 469呎 (2房)
 $1188万
 $25,339/呎
-(23年-06月-14日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
           <t>A | 957呎 (3房)
 $2278万
 $23,800/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -33793,7 +33793,7 @@
           <t>B | 525呎 (2房)
 $1421万
 $27,074/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -33801,7 +33801,7 @@
           <t>C | 522呎 (2房)
 $1404万
 $26,906/呎
-(23年-06月-18日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -33809,7 +33809,7 @@
           <t>D | 936呎 (3房)
 $2253万
 $24,076/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -33817,7 +33817,7 @@
           <t>E | 469呎 (2房)
 $1195万
 $25,473/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33832,7 +33832,7 @@
           <t>A | 957呎 (3房)
 $2292万
 $23,950/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -33840,7 +33840,7 @@
           <t>B | 525呎 (2房)
 $1400万
 $26,675/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -33848,7 +33848,7 @@
           <t>C | 522呎 (2房)
 $1384万
 $26,508/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -33856,7 +33856,7 @@
           <t>D | 936呎 (3房)
 $2183万
 $23,325/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -33864,7 +33864,7 @@
           <t>E | 469呎 (2房)
 $1131万
 $24,123/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33879,7 +33879,7 @@
           <t>A | 957呎 (3房)
 $2263万
 $23,650/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -33887,7 +33887,7 @@
           <t>B | 525呎 (2房)
 $1356万
 $25,831/呎
-(23年-06月-19日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -33895,7 +33895,7 @@
           <t>C | 522呎 (2房)
 $1172万
 $22,452/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -33903,7 +33903,7 @@
           <t>D | 936呎 (3房)
 $2155万
 $23,025/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -33911,7 +33911,7 @@
           <t>E | 469呎 (2房)
 $1109万
 $23,649/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33926,7 +33926,7 @@
           <t>A | 957呎 (3房)
 $2235万
 $23,350/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -33934,7 +33934,7 @@
           <t>B | 525呎 (2房)
 $1045万
 $19,909/呎
-(25年-05月-11日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -33942,7 +33942,7 @@
           <t>C | 522呎 (2房)
 $1162万
 $22,258/呎
-(25年-05月-28日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -33950,7 +33950,7 @@
           <t>D | 936呎 (3房)
 $2169万
 $23,175/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -33958,7 +33958,7 @@
           <t>E | 469呎 (2房)
 $1087万
 $23,186/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -33973,7 +33973,7 @@
           <t>A | 957呎 (3房)
 $2220万
 $23,200/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -33981,7 +33981,7 @@
           <t>B | 525呎 (2房)
 $1275万
 $24,279/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -33989,7 +33989,7 @@
           <t>C | 522呎 (2房)
 $1304万
 $24,979/呎
-(23年-06月-29日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -33997,7 +33997,7 @@
           <t>D | 936呎 (3房)
 $2174万
 $23,225/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -34005,7 +34005,7 @@
           <t>E | 469呎 (2房)
 $1085万
 $23,132/呎
-(23年-06月-27日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34020,7 @@
           <t>A | 914呎 (3房)
 $2422万
 $26,500/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>B | 482呎 (2房)
 $1170万
 $24,281/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>C | 479呎 (2房)
 $1186万
 $24,768/呎
-(25年-05月-26日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -34044,7 +34044,7 @@
           <t>D | 894呎 (3房)
 $2771万
 $31,000/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -34052,7 +34052,7 @@
           <t>E | 431呎 (2房)
 $1183万
 $27,437/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -29279,7 +29279,7 @@
           <t>B | 1564呎 (4+房)
 $7273万
 $46,500/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -29299,7 +29299,7 @@
           <t>A | 968呎 (3房)
 $3533万
 $36,500/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -29307,7 +29307,7 @@
           <t>B | 591呎 (2房)
 $2075万
 $35,105/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>C | 591呎 (2房)
 $2075万
 $35,105/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>D | 996呎 (3房)
 $4034万
 $40,500/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -29341,7 +29341,7 @@
           <t>A | 968呎 (3房)
 $3485万
 $36,000/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -29349,7 +29349,7 @@
           <t>B | 591呎 (2房)
 $2130万
 $36,045/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -29357,7 +29357,7 @@
           <t>C | 591呎 (2房)
 $2066万
 $34,964/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -29365,7 +29365,7 @@
           <t>D | 996呎 (3房)
 $3984万
 $40,000/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -29383,7 +29383,7 @@
           <t>A | 968呎 (3房)
 $11280万
 $116,529/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -29391,7 +29391,7 @@
           <t>B | 591呎 (2房)
 $11280万
 $190,863/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -29399,7 +29399,7 @@
           <t>C | 591呎 (2房)
 $11280万
 $190,863/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -29407,7 +29407,7 @@
           <t>D | 996呎 (3房)
 $11280万
 $113,253/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -29425,7 +29425,7 @@
           <t>A | 968呎 (3房)
 $3509万
 $36,250/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -29433,7 +29433,7 @@
           <t>B | 591呎 (2房)
 $2002万
 $33,871/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -29441,7 +29441,7 @@
           <t>C | 591呎 (2房)
 $2002万
 $33,871/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -29449,7 +29449,7 @@
           <t>D | 996呎 (3房)
 $3884万
 $39,000/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -29467,7 +29467,7 @@
           <t>A | 968呎 (3房)
 $3320万
 $34,298/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -29475,7 +29475,7 @@
           <t>B | 591呎 (2房)
 $1970万
 $33,337/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -29483,7 +29483,7 @@
           <t>C | 591呎 (2房)
 $1970万
 $33,337/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -29491,7 +29491,7 @@
           <t>D | 996呎 (3房)
 $3830万
 $38,454/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -29509,7 +29509,7 @@
           <t>A | 968呎 (3房)
 $3272万
 $33,800/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -29517,7 +29517,7 @@
           <t>B | 591呎 (2房)
 $1939万
 $32,813/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -29525,7 +29525,7 @@
           <t>C | 591呎 (2房)
 $1939万
 $32,813/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -29533,7 +29533,7 @@
           <t>D | 996呎 (3房)
 $3795万
 $38,100/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
           <t>A | 968呎 (3房)
 $3223万
 $33,300/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -29559,7 +29559,7 @@
           <t>B | 525呎 (2房)
 $1909万
 $36,356/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -29567,7 +29567,7 @@
           <t>C | 591呎 (2房)
 $1909万
 $32,296/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -29575,7 +29575,7 @@
           <t>D | 996呎 (3房)
 $3792万
 $38,071/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -29593,7 +29593,7 @@
           <t>A | 968呎 (3房)
 $3293万
 $34,021/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -29601,7 +29601,7 @@
           <t>B | 591呎 (2房)
 $1879万
 $31,788/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -29609,7 +29609,7 @@
           <t>C | 591呎 (2房)
 $1879万
 $31,788/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -29617,7 +29617,7 @@
           <t>D | 996呎 (3房)
 $3741万
 $37,563/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -29635,7 +29635,7 @@
           <t>A | 968呎 (3房)
 $3533万
 $36,500/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -29643,7 +29643,7 @@
           <t>B | 591呎 (2房)
 $1956万
 $33,093/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -29651,7 +29651,7 @@
           <t>C | 591呎 (2房)
 $2081万
 $35,212/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -29677,7 +29677,7 @@
           <t>A | 968呎 (3房)
 $3175万
 $32,800/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -29685,7 +29685,7 @@
           <t>B | 591呎 (2房)
 $1891万
 $31,995/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -29693,7 +29693,7 @@
           <t>C | 591呎 (2房)
 $1891万
 $31,995/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -29701,7 +29701,7 @@
           <t>D | 996呎 (3房)
 $3486万
 $35,000/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -29719,7 +29719,7 @@
           <t>A | 968呎 (3房)
 $3078万
 $31,798/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -29727,7 +29727,7 @@
           <t>B | 591呎 (2房)
 $1853万
 $31,346/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -29735,7 +29735,7 @@
           <t>C | 591呎 (2房)
 $1853万
 $31,346/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -29743,7 +29743,7 @@
           <t>D | 996呎 (3房)
 $3436万
 $34,500/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -29761,7 +29761,7 @@
           <t>A | 968呎 (3房)
 $3030万
 $31,300/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -29769,7 +29769,7 @@
           <t>B | 591呎 (2房)
 $1842万
 $31,159/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -29777,7 +29777,7 @@
           <t>C | 591呎 (2房)
 $1842万
 $31,159/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -29785,7 +29785,7 @@
           <t>D | 996呎 (3房)
 $3436万
 $34,500/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -29803,7 +29803,7 @@
           <t>A | 968呎 (3房)
 $2981万
 $30,800/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -29811,7 +29811,7 @@
           <t>B | 591呎 (2房)
 $1832万
 $31,004/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -29819,7 +29819,7 @@
           <t>C | 591呎 (2房)
 $1832万
 $31,004/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -29827,7 +29827,7 @@
           <t>D | 996呎 (3房)
 $3406万
 $34,200/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
           <t>A | 968呎 (3房)
 $2933万
 $30,300/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -29853,7 +29853,7 @@
           <t>B | 591呎 (2房)
 $1934万
 $32,726/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29861,7 +29861,7 @@
           <t>C | 591呎 (2房)
 $1866万
 $31,576/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -29869,7 +29869,7 @@
           <t>D | 996呎 (3房)
 $3685万
 $37,000/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -29887,7 +29887,7 @@
           <t>A | 968呎 (3房)
 $2885万
 $29,800/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -29895,7 +29895,7 @@
           <t>B | 591呎 (2房)
 $1924万
 $32,563/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -29903,7 +29903,7 @@
           <t>C | 591呎 (2房)
 $1814万
 $30,696/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -29911,7 +29911,7 @@
           <t>D | 996呎 (3房)
 $3546万
 $35,600/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -29929,7 +29929,7 @@
           <t>A | 968呎 (3房)
 $2885万
 $29,800/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -29937,7 +29937,7 @@
           <t>B | 591呎 (2房)
 $1906万
 $32,242/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29945,7 +29945,7 @@
           <t>C | 591呎 (2房)
 $1796万
 $30,393/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -29971,7 +29971,7 @@
           <t>A | 968呎 (3房)
 $2875万
 $29,700/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29979,7 +29979,7 @@
           <t>B | 591呎 (2房)
 $1817万
 $30,748/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -29987,7 +29987,7 @@
           <t>C | 591呎 (2房)
 $1747万
 $29,564/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -30013,7 +30013,7 @@
           <t>A | 968呎 (3房)
 $2768万
 $28,600/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -30021,7 +30021,7 @@
           <t>B | 591呎 (2房)
 $1685万
 $28,505/呎
-(25年-05月)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -30029,7 +30029,7 @@
           <t>C | 591呎 (2房)
 $1685万
 $28,505/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -30055,7 +30055,7 @@
           <t>A | 968呎 (3房)
 $2860万
 $29,550/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -30071,7 +30071,7 @@
           <t>C | 591呎 (2房)
 $1663万
 $28,141/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -30097,7 +30097,7 @@
           <t>A | 968呎 (3房)
 $2681万
 $27,700/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -30105,7 +30105,7 @@
           <t>B | 591呎 (2房)
 $1671万
 $28,279/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -30113,7 +30113,7 @@
           <t>C | 591呎 (2房)
 $1623万
 $27,454/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -30155,7 +30155,7 @@
           <t>C | 591呎 (2房)
 $1583万
 $26,784/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -30189,7 +30189,7 @@
           <t>B | 591呎 (2房)
 $1583万
 $26,785/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -30197,7 +30197,7 @@
           <t>C | 591呎 (2房)
 $1537万
 $26,005/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -30231,7 +30231,7 @@
           <t>B | 548呎 (2房)
 $1660万
 $30,292/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -30239,7 +30239,7 @@
           <t>C | 548呎 (2房)
 $1708万
 $31,168/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -30247,7 +30247,7 @@
           <t>D | 953呎 (3房)
 $3383万
 $35,500/呎
-(23年-07月)</t>
+(23年-07月-04日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
@@ -30437,7 +30437,7 @@
           <t>B | 333呎 (1房)
 $835万
 $25,061/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -30445,7 +30445,7 @@
           <t>C | 338呎 (1房)
 $839万
 $24,820/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -30453,7 +30453,7 @@
           <t>D | 541呎 (2房)
 $1460万
 $26,995/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -30461,7 +30461,7 @@
           <t>E | 364呎 (1房)
 $987万
 $27,116/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -30476,7 +30476,7 @@
           <t>A | 959呎 (3房)
 $2976万
 $31,032/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30484,7 +30484,7 @@
           <t>B | 333呎 (1房)
 $775万
 $23,260/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -30492,7 +30492,7 @@
           <t>C | 338呎 (1房)
 $779万
 $23,058/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -30500,7 +30500,7 @@
           <t>D | 541呎 (2房)
 $1373万
 $25,380/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -30508,7 +30508,7 @@
           <t>E | 364呎 (1房)
 $893万
 $24,524/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -30523,7 +30523,7 @@
           <t>A | 960呎 (3房)
 $3201万
 $33,348/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30531,7 +30531,7 @@
           <t>B | 333呎 (1房)
 $770万
 $23,119/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -30539,7 +30539,7 @@
           <t>C | 338呎 (1房)
 $775万
 $22,918/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -30547,7 +30547,7 @@
           <t>D | 541呎 (2房)
 $1360万
 $25,130/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -30555,7 +30555,7 @@
           <t>E | 364呎 (1房)
 $765万
 $21,026/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -30570,7 +30570,7 @@
           <t>A | 959呎 (3房)
 $2880万
 $30,031/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -30578,7 +30578,7 @@
           <t>B | 333呎 (1房)
 $768万
 $23,048/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -30586,7 +30586,7 @@
           <t>C | 338呎 (1房)
 $772万
 $22,851/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -30594,7 +30594,7 @@
           <t>D | 541呎 (2房)
 $1394万
 $25,769/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -30602,7 +30602,7 @@
           <t>E | 364呎 (1房)
 $887万
 $24,377/呎
-(23年-09月)</t>
+(23年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
           <t>A | 960呎 (3房)
 $2832万
 $29,500/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30625,7 +30625,7 @@
           <t>B | 333呎 (1房)
 $765万
 $22,980/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -30633,7 +30633,7 @@
           <t>C | 338呎 (1房)
 $770万
 $22,782/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -30641,7 +30641,7 @@
           <t>D | 541呎 (2房)
 $1333万
 $24,635/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -30649,7 +30649,7 @@
           <t>E | 364呎 (1房)
 $895万
 $24,590/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30664,7 @@
           <t>A | 960呎 (3房)
 $3098万
 $32,266/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -30672,7 +30672,7 @@
           <t>B | 333呎 (1房)
 $763万
 $22,912/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -30680,7 +30680,7 @@
           <t>C | 338呎 (1房)
 $768万
 $22,715/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -30688,7 +30688,7 @@
           <t>D | 541呎 (2房)
 $1320万
 $24,391/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -30696,7 +30696,7 @@
           <t>E | 364呎 (1房)
 $913万
 $25,085/呎
-(23年-06月)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
           <t>A | 960呎 (3房)
 $2736万
 $28,500/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30719,7 +30719,7 @@
           <t>B | 333呎 (1房)
 $761万
 $22,841/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -30727,7 +30727,7 @@
           <t>C | 338呎 (1房)
 $765万
 $22,645/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -30735,7 +30735,7 @@
           <t>D | 541呎 (2房)
 $1307万
 $24,150/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -30743,7 +30743,7 @@
           <t>E | 365呎 (1房)
 $910万
 $24,941/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -30758,7 +30758,7 @@
           <t>A | 960呎 (3房)
 $2771万
 $28,866/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30766,7 +30766,7 @@
           <t>B | 333呎 (1房)
 $758万
 $22,776/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -30774,7 +30774,7 @@
           <t>C | 338呎 (1房)
 $763万
 $22,578/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -30782,7 +30782,7 @@
           <t>D | 541呎 (2房)
 $1294万
 $23,911/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -30790,7 +30790,7 @@
           <t>E | 364呎 (1房)
 $908万
 $24,937/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -30805,7 +30805,7 @@
           <t>A | 960呎 (3房)
 $2659万
 $27,700/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -30813,7 +30813,7 @@
           <t>B | 333呎 (1房)
 $764万
 $22,942/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -30821,7 +30821,7 @@
           <t>C | 943呎 (1房)
 $761万
 $8,069/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -30829,7 +30829,7 @@
           <t>D | 541呎 (2房)
 $1281万
 $23,674/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -30837,7 +30837,7 @@
           <t>E | 364呎 (1房)
 $905万
 $24,862/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -30852,7 +30852,7 @@
           <t>A | 960呎 (3房)
 $2707万
 $28,196/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -30860,7 +30860,7 @@
           <t>B | 333呎 (1房)
 $762万
 $22,871/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -30868,7 +30868,7 @@
           <t>C | 338呎 (1房)
 $759万
 $22,441/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -30876,7 +30876,7 @@
           <t>D | 541呎 (2房)
 $1253万
 $23,160/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -30884,7 +30884,7 @@
           <t>E | 364呎 (1房)
 $872万
 $23,942/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -30899,7 +30899,7 @@
           <t>A | 960呎 (3房)
 $2592万
 $27,000/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30907,7 +30907,7 @@
           <t>B | 333呎 (1房)
 $757万
 $22,742/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -30915,7 +30915,7 @@
           <t>C | 338呎 (1房)
 $759万
 $22,441/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -30923,7 +30923,7 @@
           <t>D | 541呎 (2房)
 $1253万
 $23,160/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -30931,7 +30931,7 @@
           <t>E | 364呎 (1房)
 $902万
 $24,787/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -30946,7 +30946,7 @@
           <t>A | 960呎 (3房)
 $3058万
 $31,854/呎
-(23年-08月)</t>
+(23年-08月-08日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -30954,7 +30954,7 @@
           <t>B | 333呎 (1房)
 $749万
 $22,503/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -30962,7 +30962,7 @@
           <t>C | 338呎 (1房)
 $754万
 $22,309/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -30970,7 +30970,7 @@
           <t>D | 541呎 (2房)
 $1228万
 $22,700/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -30978,7 +30978,7 @@
           <t>E | 365呎 (1房)
 $897万
 $24,570/呎
-(23年-07月)</t>
+(23年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -30993,7 +30993,7 @@
           <t>A | 960呎 (3房)
 $2544万
 $26,500/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -31001,7 +31001,7 @@
           <t>B | 333呎 (1房)
 $747万
 $22,438/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -31009,7 +31009,7 @@
           <t>C | 338呎 (1房)
 $752万
 $22,240/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -31017,7 +31017,7 @@
           <t>D | 541呎 (2房)
 $1209万
 $22,355/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -31025,7 +31025,7 @@
           <t>E | 364呎 (1房)
 $894万
 $24,567/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
           <t>A | 960呎 (3房)
 $2515万
 $26,200/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -31048,7 +31048,7 @@
           <t>B | 333呎 (1房)
 $745万
 $22,370/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -31056,7 +31056,7 @@
           <t>C | 338呎 (1房)
 $749万
 $22,173/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -31064,7 +31064,7 @@
           <t>D | 541呎 (2房)
 $1191万
 $22,014/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -31072,7 +31072,7 @@
           <t>E | 364呎 (1房)
 $861万
 $23,657/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -31087,7 +31087,7 @@
           <t>A | 959呎 (3房)
 $2486万
 $25,927/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>B | 333呎 (1房)
 $746万
 $22,400/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -31103,7 +31103,7 @@
           <t>C | 338呎 (1房)
 $747万
 $22,108/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -31111,7 +31111,7 @@
           <t>D | 541呎 (2房)
 $1173万
 $21,674/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -31119,7 +31119,7 @@
           <t>E | 364呎 (1房)
 $888万
 $24,396/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31134,7 @@
           <t>A | 960呎 (3房)
 $2477万
 $25,800/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -31142,7 +31142,7 @@
           <t>B | 333呎 (1房)
 $740万
 $22,236/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -31150,7 +31150,7 @@
           <t>C | 338呎 (1房)
 $745万
 $22,044/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -31158,7 +31158,7 @@
           <t>D | 541呎 (2房)
 $1169万
 $21,609/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -31166,7 +31166,7 @@
           <t>E | 364呎 (1房)
 $854万
 $23,468/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31181,7 @@
           <t>A | 960呎 (3房)
 $2867万
 $29,862/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -31189,7 +31189,7 @@
           <t>B | 333呎 (1房)
 $738万
 $22,170/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -31197,7 +31197,7 @@
           <t>C | 338呎 (1房)
 $743万
 $21,977/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -31205,7 +31205,7 @@
           <t>D | 541呎 (2房)
 $1166万
 $21,543/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -31213,7 +31213,7 @@
           <t>E | 364呎 (1房)
 $880万
 $24,176/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -31228,7 +31228,7 @@
           <t>A | 960呎 (3房)
 $2924万
 $30,459/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -31236,7 +31236,7 @@
           <t>B | 333呎 (1房)
 $736万
 $22,102/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -31244,7 +31244,7 @@
           <t>C | 338呎 (1房)
 $741万
 $21,909/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -31252,7 +31252,7 @@
           <t>D | 541呎 (2房)
 $1147万
 $21,208/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -31260,7 +31260,7 @@
           <t>E | 364呎 (1房)
 $738万
 $20,262/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -31275,7 +31275,7 @@
           <t>A | 960呎 (3房)
 $2764万
 $28,788/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>B | 333呎 (1房)
 $741万
 $22,266/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>C | 338呎 (1房)
 $750万
 $22,199/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>D | 541呎 (2房)
 $1147万
 $21,208/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -31307,7 +31307,7 @@
           <t>E | 364呎 (1房)
 $863万
 $23,702/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
           <t>A | 960呎 (3房)
 $2256万
 $23,500/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -31330,7 +31330,7 @@
           <t>B | 333呎 (1房)
 $737万
 $22,129/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>C | 338呎 (1房)
 $736万
 $21,780/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>D | 541呎 (2房)
 $1144万
 $21,144/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>E | 364呎 (1房)
 $859万
 $23,586/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -31369,7 +31369,7 @@
           <t>A | 960呎 (3房)
 $2208万
 $23,000/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -31377,7 +31377,7 @@
           <t>B | 333呎 (1房)
 $737万
 $22,130/呎
-(24年-07月)</t>
+(24年-07月-09日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -31385,7 +31385,7 @@
           <t>C | 338呎 (1房)
 $734万
 $21,713/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -31393,7 +31393,7 @@
           <t>D | 541呎 (2房)
 $1126万
 $20,811/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -31401,7 +31401,7 @@
           <t>E | 364呎 (1房)
 $730万
 $20,059/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -31416,7 +31416,7 @@
           <t>A | 960呎 (3房)
 $2131万
 $22,200/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -31424,7 +31424,7 @@
           <t>B | 333呎 (1房)
 $727万
 $21,840/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -31432,7 +31432,7 @@
           <t>C | 338呎 (1房)
 $732万
 $21,649/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -31440,7 +31440,7 @@
           <t>D | 541呎 (2房)
 $1086万
 $20,074/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -31448,7 +31448,7 @@
           <t>E | 364呎 (1房)
 $727万
 $19,961/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -31463,7 +31463,7 @@
           <t>A | 960呎 (3房)
 $2504万
 $26,081/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -31471,7 +31471,7 @@
           <t>B | 333呎 (1房)
 $720万
 $21,623/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -31479,7 +31479,7 @@
           <t>C | 338呎 (1房)
 $721万
 $21,323/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -31487,7 +31487,7 @@
           <t>D | 541呎 (2房)
 $1046万
 $19,342/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -31495,7 +31495,7 @@
           <t>E | 364呎 (1房)
 $809万
 $22,221/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
           <t>A | 960呎 (3房)
 $2064万
 $21,500/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -31518,7 +31518,7 @@
           <t>B | 333呎 (1房)
 $721万
 $21,639/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -31526,7 +31526,7 @@
           <t>C | 338呎 (1房)
 $711万
 $21,040/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -31534,7 +31534,7 @@
           <t>D | 541呎 (2房)
 $1022万
 $18,888/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -31542,7 +31542,7 @@
           <t>E | 364呎 (1房)
 $799万
 $21,948/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -31557,7 +31557,7 @@
           <t>A | 916呎 (3房)
 $2843万
 $31,034/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -31565,7 +31565,7 @@
           <t>B | 311呎 (1房)
 $787万
 $25,308/呎
-(24年-07月)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -31573,7 +31573,7 @@
           <t>C | 317呎 (1房)
 $805万
 $25,403/呎
-(24年-08月)</t>
+(24年-08月-28日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -31581,7 +31581,7 @@
           <t>D | 504呎 (2房)
 $1143万
 $22,688/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -31589,7 +31589,7 @@
           <t>E | 327呎 (1房)
 $863万
 $26,400/呎
-(23年-06月)</t>
+(23年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -31793,7 +31793,7 @@
           <t>A | 997呎 (3房)
 $3639万
 $36,500/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -31801,7 +31801,7 @@
           <t>B | 597呎 (2房)
 $2138万
 $35,807/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
@@ -31842,7 +31842,7 @@
           <t>B | 597呎 (2房)
 $2152万
 $36,046/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -31883,7 +31883,7 @@
           <t>B | 597呎 (2房)
 $2154万
 $36,089/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -31924,7 +31924,7 @@
           <t>B | 597呎 (2房)
 $2022万
 $33,871/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -31957,7 +31957,7 @@
           <t>A | 997呎 (3房)
 $3420万
 $34,301/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -31965,7 +31965,7 @@
           <t>B | 597呎 (2房)
 $1990万
 $33,337/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -32006,7 +32006,7 @@
           <t>B | 597呎 (2房)
 $1959万
 $32,814/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -32047,7 +32047,7 @@
           <t>B | 597呎 (2房)
 $1967万
 $32,942/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -32055,7 +32055,7 @@
           <t>C | 593呎 (2房)
 $1947万
 $32,832/呎
-(23年-12月)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -32088,7 +32088,7 @@
           <t>B | 597呎 (2房)
 $1898万
 $31,789/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -32129,7 +32129,7 @@
           <t>B | 597呎 (2房)
 $1928万
 $32,295/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -32162,7 +32162,7 @@
           <t>A | 997呎 (3房)
 $3210万
 $32,201/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -32170,7 +32170,7 @@
           <t>B | 597呎 (2房)
 $1883万
 $31,536/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
@@ -32203,7 +32203,7 @@
           <t>A | 997呎 (3房)
 $3170万
 $31,800/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -32211,7 +32211,7 @@
           <t>B | 597呎 (2房)
 $1871万
 $31,347/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
@@ -32244,7 +32244,7 @@
           <t>A | 997呎 (3房)
 $3121万
 $31,300/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -32252,7 +32252,7 @@
           <t>B | 597呎 (2房)
 $1876万
 $31,419/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -32285,7 +32285,7 @@
           <t>A | 997呎 (3房)
 $3071万
 $30,800/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -32293,7 +32293,7 @@
           <t>B | 597呎 (2房)
 $1851万
 $31,005/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -32326,7 +32326,7 @@
           <t>A | 997呎 (3房)
 $3021万
 $30,301/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -32334,7 +32334,7 @@
           <t>B | 597呎 (2房)
 $1923万
 $32,205/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -32342,7 +32342,7 @@
           <t>C | 593呎 (2房)
 $1907万
 $32,156/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -32367,7 +32367,7 @@
           <t>A | 997呎 (3房)
 $2971万
 $29,800/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -32375,7 +32375,7 @@
           <t>B | 597呎 (2房)
 $1869万
 $31,310/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -32383,7 +32383,7 @@
           <t>C | 593呎 (2房)
 $1833万
 $30,905/呎
-(23年-07月)</t>
+(23年-07月-03日)</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -32408,7 +32408,7 @@
           <t>A | 997呎 (3房)
 $2921万
 $29,301/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -32424,7 +32424,7 @@
           <t>C | 593呎 (2房)
 $1836万
 $30,960/呎
-(23年-11月)</t>
+(23年-11月-12日)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -32457,7 +32457,7 @@
           <t>B | 597呎 (2房)
 $1765万
 $29,564/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -32465,7 +32465,7 @@
           <t>C | 593呎 (2房)
 $1786万
 $30,117/呎
-(24年-02月)</t>
+(24年-02月-06日)</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -32498,7 +32498,7 @@
           <t>B | 597呎 (2房)
 $1789万
 $29,964/呎
-(23年-06月)</t>
+(23年-06月-26日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -32539,7 +32539,7 @@
           <t>B | 597呎 (2房)
 $1680万
 $28,141/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -32547,7 +32547,7 @@
           <t>C | 593呎 (2房)
 $1723万
 $29,047/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -32580,7 +32580,7 @@
           <t>B | 597呎 (2房)
 $1657万
 $27,762/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -32621,7 +32621,7 @@
           <t>B | 597呎 (2房)
 $1581万
 $26,487/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -32629,7 +32629,7 @@
           <t>C | 593呎 (2房)
 $1624万
 $27,381/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -32662,7 +32662,7 @@
           <t>B | 597呎 (2房)
 $1589万
 $26,622/呎
-(23年-07月)</t>
+(23年-07月-03日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -32670,7 +32670,7 @@
           <t>C | 593呎 (2房)
 $1576万
 $26,584/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -32719,7 +32719,7 @@
           <t>D | 949呎 (3房)
 $3421万
 $36,048/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
@@ -32748,7 +32748,7 @@
           <t>MAISON E | 940呎 (3房)
 $2880万
 $30,638/呎
-(23年-11月)</t>
+(23年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -32892,7 +32892,7 @@
           <t>A | 1144呎 (3房)
 $4777万
 $41,757/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -32900,7 +32900,7 @@
           <t>B | 425呎 (2房)
 $1384万
 $32,572/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -32908,7 +32908,7 @@
           <t>C | 425呎 (2房)
 $1357万
 $31,928/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -32924,7 +32924,7 @@
           <t>E | 469呎 (2房)
 $1314万
 $28,006/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -32947,7 +32947,7 @@
           <t>B | 525呎 (2房)
 $1399万
 $26,654/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -32955,7 +32955,7 @@
           <t>C | 522呎 (2房)
 $1483万
 $28,407/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -32963,7 +32963,7 @@
           <t>D | 936呎 (3房)
 $3064万
 $32,735/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -32971,7 +32971,7 @@
           <t>E | 469呎 (2房)
 $1270万
 $27,077/呎
-(23年-11月)</t>
+(23年-11月-02日)</t>
         </is>
       </c>
     </row>
@@ -32994,7 +32994,7 @@
           <t>B | 525呎 (2房)
 $1437万
 $27,377/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -33002,7 +33002,7 @@
           <t>C | 522呎 (2房)
 $1454万
 $27,850/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -33010,7 +33010,7 @@
           <t>D | 936呎 (3房)
 $3017万
 $32,234/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -33018,7 +33018,7 @@
           <t>E | 469呎 (2房)
 $1124万
 $23,955/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33033,7 @@
           <t>A | 957呎 (3房)
 $3067万
 $32,050/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -33041,7 +33041,7 @@
           <t>B | 525呎 (2房)
 $1345万
 $25,621/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -33049,7 +33049,7 @@
           <t>C | 522呎 (2房)
 $1425万
 $27,303/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -33057,7 +33057,7 @@
           <t>D | 936呎 (3房)
 $2970万
 $31,734/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -33065,7 +33065,7 @@
           <t>E | 469呎 (2房)
 $1117万
 $23,812/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -33088,7 +33088,7 @@
           <t>B | 525呎 (2房)
 $1319万
 $25,118/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -33096,7 +33096,7 @@
           <t>C | 522呎 (2房)
 $1410万
 $27,008/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -33104,7 +33104,7 @@
           <t>D | 936呎 (3房)
 $2783万
 $29,732/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -33112,7 +33112,7 @@
           <t>E | 469呎 (2房)
 $1110万
 $23,669/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
           <t>A | 957呎 (3房)
 $2828万
 $29,550/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -33135,7 +33135,7 @@
           <t>B | 525呎 (2房)
 $1293万
 $24,626/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -33143,7 +33143,7 @@
           <t>C | 522呎 (2房)
 $1385万
 $26,537/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -33151,7 +33151,7 @@
           <t>D | 936呎 (3房)
 $2736万
 $29,231/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -33159,7 +33159,7 @@
           <t>E | 469呎 (2房)
 $1104万
 $23,529/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33174,7 @@
           <t>A | 957呎 (3房)
 $2780万
 $29,050/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -33182,7 +33182,7 @@
           <t>B | 525呎 (2房)
 $1283万
 $24,430/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -33190,7 +33190,7 @@
           <t>C | 522呎 (2房)
 $1374万
 $26,327/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -33198,7 +33198,7 @@
           <t>D | 936呎 (3房)
 $2689万
 $28,731/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -33206,7 +33206,7 @@
           <t>E | 469呎 (2房)
 $1247万
 $26,587/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -33221,7 +33221,7 @@
           <t>A | 957呎 (3房)
 $3030万
 $31,659/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -33229,7 +33229,7 @@
           <t>B | 525呎 (2房)
 $1587万
 $30,232/呎
-(23年-12月)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -33237,7 +33237,7 @@
           <t>C | 522呎 (2房)
 $1363万
 $26,118/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -33245,7 +33245,7 @@
           <t>D | 936呎 (3房)
 $2642万
 $28,230/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -33253,7 +33253,7 @@
           <t>E | 469呎 (2房)
 $1268万
 $27,042/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33268,7 @@
           <t>A | 957呎 (3房)
 $2909万
 $30,397/呎
-(23年-06月)</t>
+(23年-06月-29日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -33276,7 +33276,7 @@
           <t>B | 525呎 (2房)
 $1247万
 $23,755/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -33284,7 +33284,7 @@
           <t>C | 522呎 (2房)
 $1240万
 $23,752/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -33292,7 +33292,7 @@
           <t>D | 936呎 (3房)
 $2595万
 $27,729/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -33300,7 +33300,7 @@
           <t>E | 469呎 (2房)
 $1090万
 $23,238/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -33315,7 +33315,7 @@
           <t>A | 957呎 (3房)
 $2994万
 $31,283/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -33323,7 +33323,7 @@
           <t>B | 525呎 (2房)
 $1237万
 $23,566/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -33331,7 +33331,7 @@
           <t>C | 522呎 (2房)
 $1491万
 $28,563/呎
-(23年-09月)</t>
+(23年-09月-24日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -33339,7 +33339,7 @@
           <t>D | 937呎 (3房)
 $2549万
 $27,200/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -33347,7 +33347,7 @@
           <t>E | 469呎 (2房)
 $1253万
 $26,721/呎
-(23年-06月)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -33362,7 +33362,7 @@
           <t>A | 957呎 (3房)
 $2589万
 $27,050/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -33370,7 +33370,7 @@
           <t>B | 525呎 (2房)
 $1237万
 $23,566/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -33378,7 +33378,7 @@
           <t>C | 522呎 (2房)
 $1230万
 $23,565/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -33386,7 +33386,7 @@
           <t>D | 937呎 (3房)
 $2502万
 $26,700/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -33394,7 +33394,7 @@
           <t>E | 469呎 (2房)
 $1232万
 $26,265/呎
-(23年-06月)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -33409,7 +33409,7 @@
           <t>A | 957呎 (3房)
 $2560万
 $26,750/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -33417,7 +33417,7 @@
           <t>B | 525呎 (2房)
 $1225万
 $23,333/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -33425,7 +33425,7 @@
           <t>C | 522呎 (2房)
 $1218万
 $23,332/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -33433,7 +33433,7 @@
           <t>D | 936呎 (3房)
 $2474万
 $26,427/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -33441,7 +33441,7 @@
           <t>E | 469呎 (2房)
 $1203万
 $25,656/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33456,7 @@
           <t>A | 957呎 (3房)
 $2874万
 $30,030/呎
-(23年-10月)</t>
+(23年-10月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -33464,7 +33464,7 @@
           <t>B | 525呎 (2房)
 $1219万
 $23,216/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -33472,7 +33472,7 @@
           <t>C | 522呎 (2房)
 $1212万
 $23,214/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -33480,7 +33480,7 @@
           <t>D | 936呎 (3房)
 $2441万
 $26,078/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -33488,7 +33488,7 @@
           <t>E | 469呎 (2房)
 $1242万
 $26,481/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33503,7 +33503,7 @@
           <t>A | 957呎 (3房)
 $2923万
 $30,544/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -33511,7 +33511,7 @@
           <t>B | 525呎 (2房)
 $1213万
 $23,101/呎
-(25年-05月)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -33519,7 +33519,7 @@
           <t>C | 522呎 (2房)
 $1206万
 $23,098/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -33527,7 +33527,7 @@
           <t>D | 936呎 (3房)
 $2417万
 $25,827/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -33535,7 +33535,7 @@
           <t>E | 469呎 (2房)
 $1238万
 $26,402/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -33550,7 +33550,7 @@
           <t>A | 957呎 (3房)
 $2474万
 $25,850/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -33558,7 +33558,7 @@
           <t>B | 525呎 (2房)
 $1250万
 $23,806/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -33566,7 +33566,7 @@
           <t>C | 522呎 (2房)
 $1257万
 $24,079/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -33574,7 +33574,7 @@
           <t>D | 936呎 (3房)
 $2389万
 $25,527/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -33582,7 +33582,7 @@
           <t>E | 469呎 (2房)
 $1231万
 $26,244/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -33597,7 +33597,7 @@
           <t>A | 957呎 (3房)
 $2445万
 $25,550/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -33605,7 +33605,7 @@
           <t>B | 525呎 (2房)
 $1490万
 $28,383/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -33613,7 +33613,7 @@
           <t>C | 522呎 (2房)
 $1230万
 $23,562/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -33621,7 +33621,7 @@
           <t>D | 937呎 (3房)
 $2361万
 $25,200/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -33629,7 +33629,7 @@
           <t>E | 469呎 (2房)
 $1224万
 $26,088/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33644,7 +33644,7 @@
           <t>A | 957呎 (3房)
 $2383万
 $24,900/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -33652,7 +33652,7 @@
           <t>B | 525呎 (2房)
 $1177万
 $22,422/呎
-(25年-05月)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -33660,7 +33660,7 @@
           <t>C | 522呎 (2房)
 $1170万
 $22,421/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -33668,7 +33668,7 @@
           <t>D | 937呎 (3房)
 $2314万
 $24,700/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -33676,7 +33676,7 @@
           <t>E | 469呎 (2房)
 $1196万
 $25,491/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33691,7 +33691,7 @@
           <t>A | 957呎 (3房)
 $2378万
 $24,850/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -33699,7 +33699,7 @@
           <t>B | 525呎 (2房)
 $1201万
 $22,880/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -33707,7 +33707,7 @@
           <t>C | 522呎 (2房)
 $1153万
 $22,088/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -33715,7 +33715,7 @@
           <t>D | 937呎 (3房)
 $2268万
 $24,200/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -33723,7 +33723,7 @@
           <t>E | 469呎 (2房)
 $1209万
 $25,779/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33738,7 +33738,7 @@
           <t>A | 957呎 (3房)
 $2349万
 $24,550/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -33746,7 +33746,7 @@
           <t>B | 525呎 (2房)
 $1143万
 $21,765/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -33754,7 +33754,7 @@
           <t>C | 522呎 (2房)
 $1136万
 $21,761/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -33762,7 +33762,7 @@
           <t>D | 936呎 (3房)
 $2239万
 $23,926/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -33770,7 +33770,7 @@
           <t>E | 469呎 (2房)
 $1188万
 $25,339/呎
-(23年-06月)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
           <t>A | 957呎 (3房)
 $2278万
 $23,800/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -33793,7 +33793,7 @@
           <t>B | 525呎 (2房)
 $1421万
 $27,074/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -33801,7 +33801,7 @@
           <t>C | 522呎 (2房)
 $1404万
 $26,906/呎
-(23年-06月)</t>
+(23年-06月-18日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -33809,7 +33809,7 @@
           <t>D | 936呎 (3房)
 $2253万
 $24,076/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -33817,7 +33817,7 @@
           <t>E | 469呎 (2房)
 $1195万
 $25,473/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -33832,7 +33832,7 @@
           <t>A | 957呎 (3房)
 $2292万
 $23,950/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -33840,7 +33840,7 @@
           <t>B | 525呎 (2房)
 $1400万
 $26,675/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -33848,7 +33848,7 @@
           <t>C | 522呎 (2房)
 $1384万
 $26,508/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -33856,7 +33856,7 @@
           <t>D | 936呎 (3房)
 $2183万
 $23,325/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -33864,7 +33864,7 @@
           <t>E | 469呎 (2房)
 $1131万
 $24,123/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33879,7 +33879,7 @@
           <t>A | 957呎 (3房)
 $2263万
 $23,650/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -33887,7 +33887,7 @@
           <t>B | 525呎 (2房)
 $1356万
 $25,831/呎
-(23年-06月)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -33895,7 +33895,7 @@
           <t>C | 522呎 (2房)
 $1172万
 $22,452/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -33903,7 +33903,7 @@
           <t>D | 936呎 (3房)
 $2155万
 $23,025/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -33911,7 +33911,7 @@
           <t>E | 469呎 (2房)
 $1109万
 $23,649/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -33926,7 +33926,7 @@
           <t>A | 957呎 (3房)
 $2235万
 $23,350/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -33934,7 +33934,7 @@
           <t>B | 525呎 (2房)
 $1045万
 $19,909/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -33942,7 +33942,7 @@
           <t>C | 522呎 (2房)
 $1162万
 $22,258/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -33950,7 +33950,7 @@
           <t>D | 936呎 (3房)
 $2169万
 $23,175/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -33958,7 +33958,7 @@
           <t>E | 469呎 (2房)
 $1087万
 $23,186/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33973,7 +33973,7 @@
           <t>A | 957呎 (3房)
 $2220万
 $23,200/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -33981,7 +33981,7 @@
           <t>B | 525呎 (2房)
 $1275万
 $24,279/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -33989,7 +33989,7 @@
           <t>C | 522呎 (2房)
 $1304万
 $24,979/呎
-(23年-06月)</t>
+(23年-06月-29日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -33997,7 +33997,7 @@
           <t>D | 936呎 (3房)
 $2174万
 $23,225/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -34005,7 +34005,7 @@
           <t>E | 469呎 (2房)
 $1085万
 $23,132/呎
-(23年-06月)</t>
+(23年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34020,7 @@
           <t>A | 914呎 (3房)
 $2422万
 $26,500/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>B | 482呎 (2房)
 $1170万
 $24,281/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>C | 479呎 (2房)
 $1186万
 $24,768/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -34044,7 +34044,7 @@
           <t>D | 894呎 (3房)
 $2771万
 $31,000/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -34052,7 +34052,7 @@
           <t>E | 431呎 (2房)
 $1183万
 $27,437/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -136,12 +136,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -292,10 +292,10 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J227" s="3" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -14915,12 +14915,12 @@
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J228" s="3" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -14985,12 +14985,12 @@
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr">
@@ -15000,12 +15000,12 @@
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15055,12 +15055,12 @@
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J230" s="3" t="inlineStr">
@@ -15070,12 +15070,12 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -29869,7 +29869,7 @@
           <t>D | 996呎 (3房)
 $3685万
 $37,000/呎
-(26年-06月-23日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -31734,20 +31734,20 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>A | 1615呎 (4+房)
+招标单位
 -
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>B | 1556呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>B | 1556呎 (4+房)
--
--
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -31761,20 +31761,20 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>A | 1615呎 (4+房)
+招标单位
 -
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>B | 1556呎 (4+房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 1556呎 (4+房)
--
--
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
           <t>A | 997呎 (3房)
 $3639万
 $36,500/呎
-(26年-06月-23日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -31801,10 +31801,10 @@
           <t>B | 597呎 (2房)
 $2138万
 $35,807/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+(26年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31812,7 +31812,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31845,7 +31845,7 @@
 (26年-06月-09日)</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31853,7 +31853,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31886,7 +31886,7 @@
 (26年-05月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31894,7 +31894,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31935,7 +31935,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31976,7 +31976,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32017,7 +32017,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32058,7 +32058,7 @@
 (23年-12月-06日)</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32099,7 +32099,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32140,7 +32140,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32173,7 +32173,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $2215万
@@ -32181,7 +32181,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32214,7 +32214,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $2202万
@@ -32222,7 +32222,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32263,7 +32263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32304,7 +32304,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32345,7 +32345,7 @@
 (23年-06月-11日)</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32386,7 +32386,7 @@
 (23年-07月-03日)</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32427,7 +32427,7 @@
 (23年-11月-12日)</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32468,7 +32468,7 @@
 (24年-02月-06日)</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32509,7 +32509,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32550,7 +32550,7 @@
 (23年-06月-14日)</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32591,7 +32591,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32632,7 +32632,7 @@
 (23年-06月-12日)</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32673,7 +32673,7 @@
 (23年-06月-12日)</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
